--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R2" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R3" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>92509</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R15" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2026,54 +2021,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>92509</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2123,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125934949</v>
+        <v>125935014</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488893</v>
+        <v>488848</v>
       </c>
       <c r="R23" t="n">
-        <v>6818884</v>
+        <v>6818924</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125935014</v>
+        <v>125934949</v>
       </c>
       <c r="B24" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488848</v>
+        <v>488893</v>
       </c>
       <c r="R24" t="n">
-        <v>6818924</v>
+        <v>6818884</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125934399</v>
+        <v>125935887</v>
       </c>
       <c r="B41" t="n">
-        <v>79585</v>
+        <v>57651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488895</v>
+        <v>488851</v>
       </c>
       <c r="R41" t="n">
-        <v>6818859</v>
+        <v>6818708</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4570,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4586,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R42" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125935887</v>
+        <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488851</v>
+        <v>488845</v>
       </c>
       <c r="R43" t="n">
-        <v>6818708</v>
+        <v>6818675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4738,11 +4743,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R48" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B49" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R49" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R50" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R51" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5542,6 +5542,3137 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125989251</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91247</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>488207</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6818985</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125984809</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>488249</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6818977</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125984672</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>488239</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6818981</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125984501</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>488242</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6819007</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125986685</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>488505</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6818935</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125988566</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78634</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>353</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>488264</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6818869</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125984440</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>488244</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6819028</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125986131</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>488444</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6818918</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125988871</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>488271</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6818822</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125989085</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>488202</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6818963</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125988445</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>488400</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6818592</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125987243</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>488354</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6818765</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125984038</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>488196</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6819100</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125988735</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>488266</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6818782</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125986119</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91192</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>488459</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6818981</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125984150</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>488206</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6819039</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125988835</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>488237</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6818903</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125986843</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>488440</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6818890</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125989221</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>488211</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6818972</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125988482</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>488376</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6818620</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125988576</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>488336</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6818701</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125988605</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78634</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>353</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>488257</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6818880</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125985181</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>488320</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6818956</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125985280</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>488376</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6818970</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125986283</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>488483</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6818970</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125983993</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>488175</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6819105</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125985190</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>488327</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6818968</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>125987019</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>488514</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6818802</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>125987994</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>488450</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6818611</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125989375</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>488248</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6819009</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>125984338</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98365</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>488234</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6819040</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>125988725</v>
+      </c>
+      <c r="B83" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>488252</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6818905</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R2" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R3" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125935502</v>
+        <v>125937533</v>
       </c>
       <c r="B5" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488799</v>
+        <v>488556</v>
       </c>
       <c r="R5" t="n">
-        <v>6818778</v>
+        <v>6818975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937533</v>
+        <v>125937741</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488556</v>
+        <v>488731</v>
       </c>
       <c r="R6" t="n">
-        <v>6818975</v>
+        <v>6818925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125937741</v>
+        <v>125935502</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488731</v>
+        <v>488799</v>
       </c>
       <c r="R7" t="n">
-        <v>6818925</v>
+        <v>6818778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
         <v>125936168</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125936684</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125935570</v>
       </c>
       <c r="B12" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B13" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R13" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R14" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>92509</v>
+        <v>92510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>125936426</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>125935224</v>
       </c>
       <c r="B20" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125933626</v>
       </c>
       <c r="B21" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125932883</v>
       </c>
       <c r="B22" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>125935014</v>
       </c>
       <c r="B23" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125934949</v>
+        <v>125937715</v>
       </c>
       <c r="B24" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488893</v>
+        <v>488709</v>
       </c>
       <c r="R24" t="n">
-        <v>6818884</v>
+        <v>6818925</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125937715</v>
+        <v>125936468</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488709</v>
+        <v>488715</v>
       </c>
       <c r="R25" t="n">
-        <v>6818925</v>
+        <v>6818694</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125936468</v>
+        <v>125934949</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488715</v>
+        <v>488893</v>
       </c>
       <c r="R26" t="n">
-        <v>6818694</v>
+        <v>6818884</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
         <v>125937037</v>
       </c>
       <c r="B27" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>125933869</v>
       </c>
       <c r="B29" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>125936438</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>125935403</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125933949</v>
+        <v>125934563</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3631,17 +3631,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488891</v>
+        <v>488882</v>
       </c>
       <c r="R32" t="n">
-        <v>6818946</v>
+        <v>6818866</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,22 +3685,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125934563</v>
+        <v>125933949</v>
       </c>
       <c r="B33" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,17 +3728,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488882</v>
+        <v>488891</v>
       </c>
       <c r="R33" t="n">
-        <v>6818866</v>
+        <v>6818946</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,12 +3782,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3797,7 +3797,7 @@
         <v>125935283</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125936448</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R36" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B37" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R37" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B38" t="n">
-        <v>91192</v>
+        <v>78635</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R38" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>78634</v>
+        <v>91193</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R39" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>125935537</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>125936447</v>
       </c>
       <c r="B44" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125934928</v>
+        <v>125936488</v>
       </c>
       <c r="B45" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488878</v>
+        <v>488717</v>
       </c>
       <c r="R45" t="n">
-        <v>6818892</v>
+        <v>6818649</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125936488</v>
+        <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488717</v>
+        <v>488878</v>
       </c>
       <c r="R46" t="n">
-        <v>6818649</v>
+        <v>6818892</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5063,7 +5063,7 @@
         <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R48" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R49" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R50" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B51" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R51" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125984809</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R54" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R55" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>125986685</v>
       </c>
       <c r="B56" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125988566</v>
       </c>
       <c r="B57" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6127,54 +6127,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125984440</v>
+        <v>125986131</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>78726</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488244</v>
+        <v>488444</v>
       </c>
       <c r="R58" t="n">
-        <v>6819028</v>
+        <v>6818918</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6233,10 +6224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125986131</v>
+        <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>78725</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6244,34 +6235,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488444</v>
+        <v>488271</v>
       </c>
       <c r="R59" t="n">
-        <v>6818918</v>
+        <v>6818822</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6330,45 +6321,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125988871</v>
+        <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>98366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488271</v>
+        <v>488244</v>
       </c>
       <c r="R60" t="n">
-        <v>6818822</v>
+        <v>6819028</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6430,7 +6430,7 @@
         <v>125989085</v>
       </c>
       <c r="B61" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>125988445</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>125984038</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6815,48 +6815,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125988735</v>
+        <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>91193</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488266</v>
+        <v>488459</v>
       </c>
       <c r="R65" t="n">
-        <v>6818782</v>
+        <v>6818981</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6900,60 +6900,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125986119</v>
+        <v>125988735</v>
       </c>
       <c r="B66" t="n">
-        <v>91192</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488459</v>
+        <v>488266</v>
       </c>
       <c r="R66" t="n">
-        <v>6818981</v>
+        <v>6818782</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6997,12 +6997,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7012,7 +7012,7 @@
         <v>125984150</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>125988835</v>
       </c>
       <c r="B68" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>125986843</v>
       </c>
       <c r="B69" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125989221</v>
+        <v>125988482</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488211</v>
+        <v>488376</v>
       </c>
       <c r="R70" t="n">
-        <v>6818972</v>
+        <v>6818620</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,22 +7385,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125988482</v>
+        <v>125989221</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7428,17 +7428,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488376</v>
+        <v>488211</v>
       </c>
       <c r="R71" t="n">
-        <v>6818620</v>
+        <v>6818972</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7482,22 +7482,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988576</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7525,14 +7525,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488336</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125988605</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
-        <v>78634</v>
+        <v>78727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7602,21 +7602,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7626,13 +7626,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488257</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818880</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7676,22 +7676,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,22 +7773,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125985280</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7816,14 +7816,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488376</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -7882,10 +7882,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125986283</v>
+        <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78726</v>
+        <v>78635</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,21 +7893,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7917,13 +7917,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488483</v>
+        <v>488257</v>
       </c>
       <c r="R76" t="n">
-        <v>6818970</v>
+        <v>6818880</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7979,10 +7979,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125983993</v>
+        <v>125987019</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>57811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,34 +7990,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488175</v>
+        <v>488514</v>
       </c>
       <c r="R77" t="n">
-        <v>6819105</v>
+        <v>6818802</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8079,7 +8079,7 @@
         <v>125985190</v>
       </c>
       <c r="B78" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8173,10 +8173,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125987019</v>
+        <v>125983993</v>
       </c>
       <c r="B79" t="n">
-        <v>57811</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488514</v>
+        <v>488175</v>
       </c>
       <c r="R79" t="n">
-        <v>6818802</v>
+        <v>6819105</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8273,7 +8273,7 @@
         <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98365</v>
+        <v>98366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>125988725</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R13" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B14" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R14" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,54 +1924,54 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B15" t="n">
-        <v>92510</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R15" t="n">
         <v>6818877</v>
@@ -2021,22 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R16" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2104,6 +2104,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,48 +2135,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>92518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R17" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2220,22 +2220,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R18" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,13 +2364,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R19" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125935014</v>
+        <v>125934949</v>
       </c>
       <c r="B23" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488848</v>
+        <v>488893</v>
       </c>
       <c r="R23" t="n">
-        <v>6818924</v>
+        <v>6818884</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125937715</v>
+        <v>125935014</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488709</v>
+        <v>488848</v>
       </c>
       <c r="R24" t="n">
-        <v>6818925</v>
+        <v>6818924</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,19 +2904,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125936468</v>
+        <v>125937715</v>
       </c>
       <c r="B25" t="n">
         <v>78968</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488715</v>
+        <v>488709</v>
       </c>
       <c r="R25" t="n">
-        <v>6818694</v>
+        <v>6818925</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125934949</v>
+        <v>125936468</v>
       </c>
       <c r="B26" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488893</v>
+        <v>488715</v>
       </c>
       <c r="R26" t="n">
-        <v>6818884</v>
+        <v>6818694</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B38" t="n">
-        <v>78635</v>
+        <v>91193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R38" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B39" t="n">
-        <v>91193</v>
+        <v>78635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R39" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R50" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R51" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B54" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R54" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R55" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6224,45 +6224,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125988871</v>
+        <v>125984440</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>98368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488271</v>
+        <v>488244</v>
       </c>
       <c r="R59" t="n">
-        <v>6818822</v>
+        <v>6819028</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6321,54 +6330,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125984440</v>
+        <v>125988871</v>
       </c>
       <c r="B60" t="n">
-        <v>98366</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488244</v>
+        <v>488271</v>
       </c>
       <c r="R60" t="n">
-        <v>6819028</v>
+        <v>6818822</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B61" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6462,13 +6462,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R61" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125987243</v>
+        <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488354</v>
+        <v>488202</v>
       </c>
       <c r="R63" t="n">
-        <v>6818765</v>
+        <v>6818963</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125986843</v>
+        <v>125988482</v>
       </c>
       <c r="B69" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,37 +7214,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488440</v>
+        <v>488376</v>
       </c>
       <c r="R69" t="n">
-        <v>6818890</v>
+        <v>6818620</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,19 +7288,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125988482</v>
+        <v>125989221</v>
       </c>
       <c r="B70" t="n">
         <v>78968</v>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488376</v>
+        <v>488211</v>
       </c>
       <c r="R70" t="n">
-        <v>6818620</v>
+        <v>6818972</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,22 +7385,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125989221</v>
+        <v>125986843</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488211</v>
+        <v>488440</v>
       </c>
       <c r="R71" t="n">
-        <v>6818972</v>
+        <v>6818890</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78727</v>
+        <v>78635</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488257</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818880</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
         <v>78727</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
         <v>78727</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
         <v>78727</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988605</v>
+        <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78635</v>
+        <v>78727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488257</v>
+        <v>488336</v>
       </c>
       <c r="R76" t="n">
-        <v>6818880</v>
+        <v>6818701</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125987019</v>
+        <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>57811</v>
+        <v>78726</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488514</v>
+        <v>488327</v>
       </c>
       <c r="R77" t="n">
-        <v>6818802</v>
+        <v>6818968</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125985190</v>
+        <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488327</v>
+        <v>488175</v>
       </c>
       <c r="R78" t="n">
-        <v>6818968</v>
+        <v>6819105</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125983993</v>
+        <v>125987019</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488175</v>
+        <v>488514</v>
       </c>
       <c r="R79" t="n">
-        <v>6819105</v>
+        <v>6818802</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -2033,48 +2033,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>92518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R16" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2104,11 +2104,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2123,60 +2118,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125934507</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>92518</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488909</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2220,12 +2220,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B36" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R36" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R37" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125935887</v>
+        <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>79586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488851</v>
+        <v>488895</v>
       </c>
       <c r="R41" t="n">
-        <v>6818708</v>
+        <v>6818859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B42" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R42" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125936025</v>
+        <v>125935887</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,34 +4678,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488845</v>
+        <v>488851</v>
       </c>
       <c r="R43" t="n">
-        <v>6818675</v>
+        <v>6818708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4743,6 +4738,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R54" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R55" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6224,54 +6224,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125984440</v>
+        <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488244</v>
+        <v>488271</v>
       </c>
       <c r="R59" t="n">
-        <v>6819028</v>
+        <v>6818822</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6330,45 +6321,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125988871</v>
+        <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>98368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488271</v>
+        <v>488244</v>
       </c>
       <c r="R60" t="n">
-        <v>6818822</v>
+        <v>6819028</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R2" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R3" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936665</v>
+        <v>125937533</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488458</v>
+        <v>488556</v>
       </c>
       <c r="R4" t="n">
-        <v>6818635</v>
+        <v>6818975</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125937533</v>
+        <v>125937741</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488556</v>
+        <v>488731</v>
       </c>
       <c r="R5" t="n">
-        <v>6818975</v>
+        <v>6818925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937741</v>
+        <v>125936168</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,17 +1094,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488731</v>
+        <v>488761</v>
       </c>
       <c r="R6" t="n">
-        <v>6818925</v>
+        <v>6818718</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125935502</v>
+        <v>125936665</v>
       </c>
       <c r="B7" t="n">
-        <v>79586</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488799</v>
+        <v>488458</v>
       </c>
       <c r="R7" t="n">
-        <v>6818778</v>
+        <v>6818635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936168</v>
+        <v>125935502</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488761</v>
+        <v>488799</v>
       </c>
       <c r="R8" t="n">
-        <v>6818718</v>
+        <v>6818778</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125936684</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125935570</v>
       </c>
       <c r="B12" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125934407</v>
       </c>
       <c r="B13" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125934762</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R15" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2036,7 +2041,7 @@
         <v>125934507</v>
       </c>
       <c r="B16" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125937897</v>
+        <v>125935510</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2170,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488805</v>
+        <v>488703</v>
       </c>
       <c r="R17" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R18" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,13 +2369,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R19" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2434,7 +2434,7 @@
         <v>125935224</v>
       </c>
       <c r="B20" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125933626</v>
       </c>
       <c r="B21" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125932883</v>
       </c>
       <c r="B22" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125934949</v>
+        <v>125937715</v>
       </c>
       <c r="B23" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488893</v>
+        <v>488709</v>
       </c>
       <c r="R23" t="n">
-        <v>6818884</v>
+        <v>6818925</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
         <v>125935014</v>
       </c>
       <c r="B24" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125937715</v>
+        <v>125936468</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488709</v>
+        <v>488715</v>
       </c>
       <c r="R25" t="n">
-        <v>6818925</v>
+        <v>6818694</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125936468</v>
+        <v>125934949</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488715</v>
+        <v>488893</v>
       </c>
       <c r="R26" t="n">
-        <v>6818694</v>
+        <v>6818884</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,22 +3098,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125937037</v>
+        <v>125937098</v>
       </c>
       <c r="B27" t="n">
-        <v>78635</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488431</v>
+        <v>488445</v>
       </c>
       <c r="R27" t="n">
-        <v>6818719</v>
+        <v>6818739</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3181,6 +3181,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3195,22 +3200,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125937098</v>
+        <v>125937037</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3223,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,13 +3247,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488445</v>
+        <v>488431</v>
       </c>
       <c r="R28" t="n">
-        <v>6818739</v>
+        <v>6818719</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3278,11 +3283,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3297,12 +3297,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
         <v>125933869</v>
       </c>
       <c r="B29" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125936438</v>
+        <v>125935403</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,17 +3437,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488735</v>
+        <v>488776</v>
       </c>
       <c r="R30" t="n">
-        <v>6818743</v>
+        <v>6818801</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3491,22 +3491,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125935403</v>
+        <v>125936438</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,17 +3534,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488776</v>
+        <v>488735</v>
       </c>
       <c r="R31" t="n">
-        <v>6818801</v>
+        <v>6818743</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125934563</v>
+        <v>125935283</v>
       </c>
       <c r="B32" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,37 +3611,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488882</v>
+        <v>488789</v>
       </c>
       <c r="R32" t="n">
-        <v>6818866</v>
+        <v>6818951</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,22 +3685,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125933949</v>
+        <v>125934563</v>
       </c>
       <c r="B33" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,17 +3728,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488891</v>
+        <v>488882</v>
       </c>
       <c r="R33" t="n">
-        <v>6818946</v>
+        <v>6818866</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,22 +3782,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125935283</v>
+        <v>125933949</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488789</v>
+        <v>488891</v>
       </c>
       <c r="R34" t="n">
-        <v>6818951</v>
+        <v>6818946</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125936448</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>125934450</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>125935216</v>
       </c>
       <c r="B37" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B38" t="n">
-        <v>91193</v>
+        <v>78639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R38" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>78635</v>
+        <v>91197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R39" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>125935537</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125934399</v>
+        <v>125935887</v>
       </c>
       <c r="B41" t="n">
-        <v>79586</v>
+        <v>57651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488895</v>
+        <v>488851</v>
       </c>
       <c r="R41" t="n">
-        <v>6818859</v>
+        <v>6818708</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4570,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4586,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R42" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125935887</v>
+        <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488851</v>
+        <v>488845</v>
       </c>
       <c r="R43" t="n">
-        <v>6818708</v>
+        <v>6818675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4738,11 +4743,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125936447</v>
+        <v>125936488</v>
       </c>
       <c r="B44" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488656</v>
+        <v>488717</v>
       </c>
       <c r="R44" t="n">
-        <v>6818762</v>
+        <v>6818649</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936488</v>
+        <v>125936447</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488717</v>
+        <v>488656</v>
       </c>
       <c r="R45" t="n">
-        <v>6818649</v>
+        <v>6818762</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,12 +4951,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
         <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125984809</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>125986685</v>
       </c>
       <c r="B56" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125988566</v>
       </c>
       <c r="B57" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>125986131</v>
       </c>
       <c r="B58" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125987243</v>
+        <v>125988445</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6458,17 +6458,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488354</v>
+        <v>488400</v>
       </c>
       <c r="R61" t="n">
-        <v>6818765</v>
+        <v>6818592</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,22 +6512,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125988445</v>
+        <v>125987243</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488400</v>
+        <v>488354</v>
       </c>
       <c r="R62" t="n">
-        <v>6818592</v>
+        <v>6818765</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,12 +6609,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
         <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>125984038</v>
       </c>
       <c r="B64" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>125988735</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>125984150</v>
       </c>
       <c r="B67" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>125988835</v>
       </c>
       <c r="B68" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>125988482</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>125989221</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>125986843</v>
       </c>
       <c r="B71" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>125985280</v>
       </c>
       <c r="B73" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>125985181</v>
       </c>
       <c r="B74" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>125986283</v>
       </c>
       <c r="B75" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8270,45 +8270,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125987994</v>
+        <v>125989375</v>
       </c>
       <c r="B80" t="n">
-        <v>78726</v>
+        <v>98372</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488450</v>
+        <v>488248</v>
       </c>
       <c r="R80" t="n">
-        <v>6818611</v>
+        <v>6819009</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8367,10 +8376,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125989375</v>
+        <v>125984338</v>
       </c>
       <c r="B81" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8397,7 +8406,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8411,10 +8420,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488248</v>
+        <v>488234</v>
       </c>
       <c r="R81" t="n">
-        <v>6819009</v>
+        <v>6819040</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8473,54 +8482,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125984338</v>
+        <v>125987994</v>
       </c>
       <c r="B82" t="n">
-        <v>98368</v>
+        <v>78730</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488234</v>
+        <v>488450</v>
       </c>
       <c r="R82" t="n">
-        <v>6819040</v>
+        <v>6818611</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8582,7 +8582,7 @@
         <v>125988725</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R15" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2026,54 +2021,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2123,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125935887</v>
+        <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488851</v>
+        <v>488895</v>
       </c>
       <c r="R41" t="n">
-        <v>6818708</v>
+        <v>6818859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R42" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125936025</v>
+        <v>125935887</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,34 +4678,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488845</v>
+        <v>488851</v>
       </c>
       <c r="R43" t="n">
-        <v>6818675</v>
+        <v>6818708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4743,6 +4738,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125934928</v>
+        <v>125932852</v>
       </c>
       <c r="B46" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488878</v>
+        <v>488802</v>
       </c>
       <c r="R46" t="n">
-        <v>6818892</v>
+        <v>6819049</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125932852</v>
+        <v>125934928</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488802</v>
+        <v>488878</v>
       </c>
       <c r="R47" t="n">
-        <v>6819049</v>
+        <v>6818892</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5145,12 +5145,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R50" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R51" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125988445</v>
+        <v>125989085</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488400</v>
+        <v>488202</v>
       </c>
       <c r="R61" t="n">
-        <v>6818592</v>
+        <v>6818963</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125987243</v>
+        <v>125988445</v>
       </c>
       <c r="B62" t="n">
         <v>78972</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488354</v>
+        <v>488400</v>
       </c>
       <c r="R62" t="n">
-        <v>6818765</v>
+        <v>6818592</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R63" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988605</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488257</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
-        <v>6818880</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985280</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
         <v>78731</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488376</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
         <v>78731</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125986283</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
         <v>78731</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488483</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988576</v>
+        <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488336</v>
+        <v>488257</v>
       </c>
       <c r="R76" t="n">
-        <v>6818701</v>
+        <v>6818880</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125985190</v>
+        <v>125987019</v>
       </c>
       <c r="B77" t="n">
-        <v>78730</v>
+        <v>57811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488327</v>
+        <v>488514</v>
       </c>
       <c r="R77" t="n">
-        <v>6818968</v>
+        <v>6818802</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R78" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125987019</v>
+        <v>125983993</v>
       </c>
       <c r="B79" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488514</v>
+        <v>488175</v>
       </c>
       <c r="R79" t="n">
-        <v>6818802</v>
+        <v>6819105</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R2" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R3" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125937533</v>
+        <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488556</v>
+        <v>488458</v>
       </c>
       <c r="R4" t="n">
-        <v>6818975</v>
+        <v>6818635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125937741</v>
+        <v>125935502</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488731</v>
+        <v>488799</v>
       </c>
       <c r="R5" t="n">
-        <v>6818925</v>
+        <v>6818778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125936168</v>
+        <v>125937321</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488761</v>
+        <v>488500</v>
       </c>
       <c r="R6" t="n">
-        <v>6818718</v>
+        <v>6818934</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125936665</v>
+        <v>125934921</v>
       </c>
       <c r="B7" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488458</v>
+        <v>488878</v>
       </c>
       <c r="R7" t="n">
-        <v>6818635</v>
+        <v>6818893</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125935502</v>
+        <v>125936684</v>
       </c>
       <c r="B8" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488799</v>
+        <v>488631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818778</v>
+        <v>6818621</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,19 +1342,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937321</v>
+        <v>125935570</v>
       </c>
       <c r="B9" t="n">
         <v>78731</v>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488500</v>
+        <v>488824</v>
       </c>
       <c r="R9" t="n">
-        <v>6818934</v>
+        <v>6818805</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125934921</v>
+        <v>125937533</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488878</v>
+        <v>488556</v>
       </c>
       <c r="R10" t="n">
-        <v>6818893</v>
+        <v>6818975</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936684</v>
+        <v>125937741</v>
       </c>
       <c r="B11" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488631</v>
+        <v>488731</v>
       </c>
       <c r="R11" t="n">
-        <v>6818621</v>
+        <v>6818925</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125935570</v>
+        <v>125936168</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488824</v>
+        <v>488761</v>
       </c>
       <c r="R12" t="n">
-        <v>6818805</v>
+        <v>6818718</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B13" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R13" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R14" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R18" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,13 +2364,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R19" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125935014</v>
+        <v>125936468</v>
       </c>
       <c r="B24" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488848</v>
+        <v>488715</v>
       </c>
       <c r="R24" t="n">
-        <v>6818924</v>
+        <v>6818694</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,22 +2904,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125936468</v>
+        <v>125935014</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488715</v>
+        <v>488848</v>
       </c>
       <c r="R25" t="n">
-        <v>6818694</v>
+        <v>6818924</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125937098</v>
+        <v>125937037</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488445</v>
+        <v>488431</v>
       </c>
       <c r="R27" t="n">
-        <v>6818739</v>
+        <v>6818719</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3181,11 +3181,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3200,22 +3195,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125937037</v>
+        <v>125937098</v>
       </c>
       <c r="B28" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3223,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3247,13 +3242,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488431</v>
+        <v>488445</v>
       </c>
       <c r="R28" t="n">
-        <v>6818719</v>
+        <v>6818739</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3283,6 +3278,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3297,12 +3297,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125935403</v>
+        <v>125936438</v>
       </c>
       <c r="B30" t="n">
         <v>78972</v>
@@ -3437,17 +3437,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488776</v>
+        <v>488735</v>
       </c>
       <c r="R30" t="n">
-        <v>6818801</v>
+        <v>6818743</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3491,19 +3491,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125936438</v>
+        <v>125935403</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3534,17 +3534,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488735</v>
+        <v>488776</v>
       </c>
       <c r="R31" t="n">
-        <v>6818743</v>
+        <v>6818801</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3588,12 +3588,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R36" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B37" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R37" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B38" t="n">
-        <v>78639</v>
+        <v>91197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R38" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B39" t="n">
-        <v>91197</v>
+        <v>78639</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R39" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R41" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R42" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125932852</v>
+        <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488802</v>
+        <v>488878</v>
       </c>
       <c r="R46" t="n">
-        <v>6819049</v>
+        <v>6818892</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125934928</v>
+        <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488878</v>
+        <v>488802</v>
       </c>
       <c r="R47" t="n">
-        <v>6818892</v>
+        <v>6819049</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5145,22 +5145,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R48" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R49" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R50" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R51" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125988482</v>
+        <v>125986843</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,37 +7214,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488376</v>
+        <v>488440</v>
       </c>
       <c r="R69" t="n">
-        <v>6818620</v>
+        <v>6818890</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,19 +7288,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125989221</v>
+        <v>125988482</v>
       </c>
       <c r="B70" t="n">
         <v>78972</v>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488211</v>
+        <v>488376</v>
       </c>
       <c r="R70" t="n">
-        <v>6818972</v>
+        <v>6818620</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,22 +7385,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125986843</v>
+        <v>125989221</v>
       </c>
       <c r="B71" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488440</v>
+        <v>488211</v>
       </c>
       <c r="R71" t="n">
-        <v>6818890</v>
+        <v>6818972</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488257</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818880</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
         <v>78731</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
         <v>78731</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
         <v>78731</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988605</v>
+        <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488257</v>
+        <v>488336</v>
       </c>
       <c r="R76" t="n">
-        <v>6818880</v>
+        <v>6818701</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125987019</v>
+        <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>57811</v>
+        <v>78730</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488514</v>
+        <v>488327</v>
       </c>
       <c r="R77" t="n">
-        <v>6818802</v>
+        <v>6818968</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125985190</v>
+        <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488327</v>
+        <v>488175</v>
       </c>
       <c r="R78" t="n">
-        <v>6818968</v>
+        <v>6819105</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125983993</v>
+        <v>125987019</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488175</v>
+        <v>488514</v>
       </c>
       <c r="R79" t="n">
-        <v>6819105</v>
+        <v>6818802</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8270,54 +8270,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125989375</v>
+        <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>98372</v>
+        <v>78730</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488248</v>
+        <v>488450</v>
       </c>
       <c r="R80" t="n">
-        <v>6819009</v>
+        <v>6818611</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8376,10 +8367,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125984338</v>
+        <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8406,7 +8397,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8420,10 +8411,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488234</v>
+        <v>488248</v>
       </c>
       <c r="R81" t="n">
-        <v>6819040</v>
+        <v>6819009</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8482,45 +8473,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125987994</v>
+        <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>78730</v>
+        <v>98373</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488450</v>
+        <v>488234</v>
       </c>
       <c r="R82" t="n">
-        <v>6818611</v>
+        <v>6819040</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R2" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R3" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936665</v>
+        <v>125937321</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488458</v>
+        <v>488500</v>
       </c>
       <c r="R4" t="n">
-        <v>6818635</v>
+        <v>6818934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125935502</v>
+        <v>125934921</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488799</v>
+        <v>488878</v>
       </c>
       <c r="R5" t="n">
-        <v>6818778</v>
+        <v>6818893</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937321</v>
+        <v>125936684</v>
       </c>
       <c r="B6" t="n">
         <v>78731</v>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488500</v>
+        <v>488631</v>
       </c>
       <c r="R6" t="n">
-        <v>6818934</v>
+        <v>6818621</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,19 +1148,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125934921</v>
+        <v>125935570</v>
       </c>
       <c r="B7" t="n">
         <v>78731</v>
@@ -1191,17 +1191,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488878</v>
+        <v>488824</v>
       </c>
       <c r="R7" t="n">
-        <v>6818893</v>
+        <v>6818805</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936684</v>
+        <v>125937533</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488631</v>
+        <v>488556</v>
       </c>
       <c r="R8" t="n">
-        <v>6818621</v>
+        <v>6818975</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125935570</v>
+        <v>125937741</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488824</v>
+        <v>488731</v>
       </c>
       <c r="R9" t="n">
-        <v>6818805</v>
+        <v>6818925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,19 +1439,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125937533</v>
+        <v>125936168</v>
       </c>
       <c r="B10" t="n">
         <v>78972</v>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488556</v>
+        <v>488761</v>
       </c>
       <c r="R10" t="n">
-        <v>6818975</v>
+        <v>6818718</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125937741</v>
+        <v>125936665</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488731</v>
+        <v>488458</v>
       </c>
       <c r="R11" t="n">
-        <v>6818925</v>
+        <v>6818635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936168</v>
+        <v>125935502</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488761</v>
+        <v>488799</v>
       </c>
       <c r="R12" t="n">
-        <v>6818718</v>
+        <v>6818778</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125934507</v>
+        <v>125937897</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488909</v>
+        <v>488805</v>
       </c>
       <c r="R15" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2021,54 +2026,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125935510</v>
+        <v>125934507</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488703</v>
+        <v>488909</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2118,22 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125937897</v>
+        <v>125935510</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2170,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488805</v>
+        <v>488703</v>
       </c>
       <c r="R17" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936447</v>
+        <v>125932852</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488656</v>
+        <v>488802</v>
       </c>
       <c r="R45" t="n">
-        <v>6818762</v>
+        <v>6819049</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,19 +4951,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125934928</v>
+        <v>125936447</v>
       </c>
       <c r="B46" t="n">
         <v>79590</v>
@@ -4994,17 +4994,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488878</v>
+        <v>488656</v>
       </c>
       <c r="R46" t="n">
-        <v>6818892</v>
+        <v>6818762</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125932852</v>
+        <v>125934928</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488802</v>
+        <v>488878</v>
       </c>
       <c r="R47" t="n">
-        <v>6819049</v>
+        <v>6818892</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5145,12 +5145,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125986843</v>
+        <v>125989221</v>
       </c>
       <c r="B69" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,21 +7214,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488440</v>
+        <v>488211</v>
       </c>
       <c r="R69" t="n">
-        <v>6818890</v>
+        <v>6818972</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125989221</v>
+        <v>125986843</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488211</v>
+        <v>488440</v>
       </c>
       <c r="R71" t="n">
-        <v>6818972</v>
+        <v>6818890</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988605</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488257</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
-        <v>6818880</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985280</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
         <v>78731</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488376</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
         <v>78731</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125986283</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
         <v>78731</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488483</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988576</v>
+        <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488336</v>
+        <v>488257</v>
       </c>
       <c r="R76" t="n">
-        <v>6818701</v>
+        <v>6818880</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125985190</v>
+        <v>125987019</v>
       </c>
       <c r="B77" t="n">
-        <v>78730</v>
+        <v>57811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488327</v>
+        <v>488514</v>
       </c>
       <c r="R77" t="n">
-        <v>6818968</v>
+        <v>6818802</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R78" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125987019</v>
+        <v>125983993</v>
       </c>
       <c r="B79" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488514</v>
+        <v>488175</v>
       </c>
       <c r="R79" t="n">
-        <v>6818802</v>
+        <v>6819105</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125937321</v>
+        <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488500</v>
+        <v>488458</v>
       </c>
       <c r="R4" t="n">
-        <v>6818934</v>
+        <v>6818635</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125934921</v>
+        <v>125935502</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488878</v>
+        <v>488799</v>
       </c>
       <c r="R5" t="n">
-        <v>6818893</v>
+        <v>6818778</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125936684</v>
+        <v>125937321</v>
       </c>
       <c r="B6" t="n">
         <v>78731</v>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488631</v>
+        <v>488500</v>
       </c>
       <c r="R6" t="n">
-        <v>6818621</v>
+        <v>6818934</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,19 +1148,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125935570</v>
+        <v>125934921</v>
       </c>
       <c r="B7" t="n">
         <v>78731</v>
@@ -1191,17 +1191,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488824</v>
+        <v>488878</v>
       </c>
       <c r="R7" t="n">
-        <v>6818805</v>
+        <v>6818893</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125937533</v>
+        <v>125936684</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488556</v>
+        <v>488631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818975</v>
+        <v>6818621</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937741</v>
+        <v>125935570</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488731</v>
+        <v>488824</v>
       </c>
       <c r="R9" t="n">
-        <v>6818925</v>
+        <v>6818805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,19 +1439,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125936168</v>
+        <v>125937533</v>
       </c>
       <c r="B10" t="n">
         <v>78972</v>
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488761</v>
+        <v>488556</v>
       </c>
       <c r="R10" t="n">
-        <v>6818718</v>
+        <v>6818975</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936665</v>
+        <v>125937741</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488458</v>
+        <v>488731</v>
       </c>
       <c r="R11" t="n">
-        <v>6818635</v>
+        <v>6818925</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125935502</v>
+        <v>125936168</v>
       </c>
       <c r="B12" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488799</v>
+        <v>488761</v>
       </c>
       <c r="R12" t="n">
-        <v>6818778</v>
+        <v>6818718</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>92522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R15" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2026,54 +2021,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2123,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R18" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,13 +2369,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R19" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125932852</v>
+        <v>125936447</v>
       </c>
       <c r="B45" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488802</v>
+        <v>488656</v>
       </c>
       <c r="R45" t="n">
-        <v>6819049</v>
+        <v>6818762</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,19 +4951,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125936447</v>
+        <v>125934928</v>
       </c>
       <c r="B46" t="n">
         <v>79590</v>
@@ -4994,17 +4994,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488656</v>
+        <v>488878</v>
       </c>
       <c r="R46" t="n">
-        <v>6818762</v>
+        <v>6818892</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125934928</v>
+        <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488878</v>
+        <v>488802</v>
       </c>
       <c r="R47" t="n">
-        <v>6818892</v>
+        <v>6819049</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5145,12 +5145,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -7979,10 +7979,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125987019</v>
+        <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>57811</v>
+        <v>78730</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488514</v>
+        <v>488327</v>
       </c>
       <c r="R77" t="n">
-        <v>6818802</v>
+        <v>6818968</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125985190</v>
+        <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488327</v>
+        <v>488175</v>
       </c>
       <c r="R78" t="n">
-        <v>6818968</v>
+        <v>6819105</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125983993</v>
+        <v>125987019</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488175</v>
+        <v>488514</v>
       </c>
       <c r="R79" t="n">
-        <v>6819105</v>
+        <v>6818802</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R2" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R3" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125935502</v>
+        <v>125937533</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488799</v>
+        <v>488556</v>
       </c>
       <c r="R5" t="n">
-        <v>6818778</v>
+        <v>6818975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937321</v>
+        <v>125937741</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488500</v>
+        <v>488731</v>
       </c>
       <c r="R6" t="n">
-        <v>6818934</v>
+        <v>6818925</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125934921</v>
+        <v>125935502</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488878</v>
+        <v>488799</v>
       </c>
       <c r="R7" t="n">
-        <v>6818893</v>
+        <v>6818778</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936684</v>
+        <v>125936168</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488631</v>
+        <v>488761</v>
       </c>
       <c r="R8" t="n">
-        <v>6818621</v>
+        <v>6818718</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125935570</v>
+        <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488824</v>
+        <v>488500</v>
       </c>
       <c r="R9" t="n">
-        <v>6818805</v>
+        <v>6818934</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125937533</v>
+        <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488556</v>
+        <v>488878</v>
       </c>
       <c r="R10" t="n">
-        <v>6818975</v>
+        <v>6818893</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125937741</v>
+        <v>125936684</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488731</v>
+        <v>488631</v>
       </c>
       <c r="R11" t="n">
-        <v>6818925</v>
+        <v>6818621</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936168</v>
+        <v>125935570</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488761</v>
+        <v>488824</v>
       </c>
       <c r="R12" t="n">
-        <v>6818718</v>
+        <v>6818805</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R13" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B14" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R14" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R18" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,13 +2364,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R19" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2434,7 +2434,7 @@
         <v>125935224</v>
       </c>
       <c r="B20" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125933626</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125932883</v>
       </c>
       <c r="B22" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125937715</v>
+        <v>125935014</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488709</v>
+        <v>488848</v>
       </c>
       <c r="R23" t="n">
-        <v>6818925</v>
+        <v>6818924</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125936468</v>
+        <v>125937715</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488715</v>
+        <v>488709</v>
       </c>
       <c r="R24" t="n">
-        <v>6818694</v>
+        <v>6818925</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125935014</v>
+        <v>125936468</v>
       </c>
       <c r="B25" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,37 +2927,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488848</v>
+        <v>488715</v>
       </c>
       <c r="R25" t="n">
-        <v>6818924</v>
+        <v>6818694</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3016,7 +3016,7 @@
         <v>125934949</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125937037</v>
+        <v>125937098</v>
       </c>
       <c r="B27" t="n">
-        <v>78639</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488431</v>
+        <v>488445</v>
       </c>
       <c r="R27" t="n">
-        <v>6818719</v>
+        <v>6818739</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3181,6 +3181,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3195,22 +3200,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125937098</v>
+        <v>125937037</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>78640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3223,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,13 +3247,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488445</v>
+        <v>488431</v>
       </c>
       <c r="R28" t="n">
-        <v>6818739</v>
+        <v>6818719</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3278,11 +3283,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3297,12 +3297,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
         <v>125933869</v>
       </c>
       <c r="B29" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>125936438</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>125935403</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125935283</v>
+        <v>125934563</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,37 +3611,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488789</v>
+        <v>488882</v>
       </c>
       <c r="R32" t="n">
-        <v>6818951</v>
+        <v>6818866</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,22 +3685,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125934563</v>
+        <v>125933949</v>
       </c>
       <c r="B33" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,17 +3728,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488882</v>
+        <v>488891</v>
       </c>
       <c r="R33" t="n">
-        <v>6818866</v>
+        <v>6818946</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,22 +3782,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125933949</v>
+        <v>125935283</v>
       </c>
       <c r="B34" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488891</v>
+        <v>488789</v>
       </c>
       <c r="R34" t="n">
-        <v>6818946</v>
+        <v>6818951</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125936448</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B36" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R36" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R37" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4185,7 +4185,7 @@
         <v>125933758</v>
       </c>
       <c r="B38" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>125934468</v>
       </c>
       <c r="B39" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>125935537</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R41" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B42" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R42" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4670,7 +4670,7 @@
         <v>125935887</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125936488</v>
+        <v>125936447</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488717</v>
+        <v>488656</v>
       </c>
       <c r="R44" t="n">
-        <v>6818649</v>
+        <v>6818762</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936447</v>
+        <v>125936488</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488656</v>
+        <v>488717</v>
       </c>
       <c r="R45" t="n">
-        <v>6818762</v>
+        <v>6818649</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,12 +4951,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
         <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R48" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R49" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5354,7 +5354,7 @@
         <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125984809</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>125986685</v>
       </c>
       <c r="B56" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125988566</v>
       </c>
       <c r="B57" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6127,45 +6127,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125986131</v>
+        <v>125984440</v>
       </c>
       <c r="B58" t="n">
-        <v>78730</v>
+        <v>98375</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488444</v>
+        <v>488244</v>
       </c>
       <c r="R58" t="n">
-        <v>6818918</v>
+        <v>6819028</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6224,10 +6233,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125988871</v>
+        <v>125986131</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,34 +6244,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488271</v>
+        <v>488444</v>
       </c>
       <c r="R59" t="n">
-        <v>6818822</v>
+        <v>6818918</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6321,54 +6330,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125984440</v>
+        <v>125988871</v>
       </c>
       <c r="B60" t="n">
-        <v>98373</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488244</v>
+        <v>488271</v>
       </c>
       <c r="R60" t="n">
-        <v>6819028</v>
+        <v>6818822</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6430,7 +6430,7 @@
         <v>125989085</v>
       </c>
       <c r="B61" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>125988445</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>125984038</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>125988735</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>125984150</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>125988835</v>
       </c>
       <c r="B68" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125989221</v>
+        <v>125988482</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7234,17 +7234,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488211</v>
+        <v>488376</v>
       </c>
       <c r="R69" t="n">
-        <v>6818972</v>
+        <v>6818620</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,22 +7288,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125988482</v>
+        <v>125989221</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488376</v>
+        <v>488211</v>
       </c>
       <c r="R70" t="n">
-        <v>6818620</v>
+        <v>6818972</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,12 +7385,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7400,7 +7400,7 @@
         <v>125986843</v>
       </c>
       <c r="B71" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488257</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818880</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,22 +7579,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,10 +7688,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,22 +7773,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988605</v>
+        <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488257</v>
+        <v>488336</v>
       </c>
       <c r="R76" t="n">
-        <v>6818880</v>
+        <v>6818701</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,12 +7967,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -7982,7 +7982,7 @@
         <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>125987019</v>
       </c>
       <c r="B79" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>125988725</v>
       </c>
       <c r="B83" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B38" t="n">
-        <v>91199</v>
+        <v>78640</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R38" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>78640</v>
+        <v>91199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R39" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125936447</v>
+        <v>125934928</v>
       </c>
       <c r="B44" t="n">
         <v>79591</v>
@@ -4800,17 +4800,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488656</v>
+        <v>488878</v>
       </c>
       <c r="R44" t="n">
-        <v>6818762</v>
+        <v>6818892</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936488</v>
+        <v>125936447</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488717</v>
+        <v>488656</v>
       </c>
       <c r="R45" t="n">
-        <v>6818649</v>
+        <v>6818762</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125934928</v>
+        <v>125936488</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488878</v>
+        <v>488717</v>
       </c>
       <c r="R46" t="n">
-        <v>6818892</v>
+        <v>6818649</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B54" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R54" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R55" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6127,54 +6127,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125984440</v>
+        <v>125986131</v>
       </c>
       <c r="B58" t="n">
-        <v>98375</v>
+        <v>78731</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488244</v>
+        <v>488444</v>
       </c>
       <c r="R58" t="n">
-        <v>6819028</v>
+        <v>6818918</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6233,10 +6224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125986131</v>
+        <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6244,34 +6235,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488444</v>
+        <v>488271</v>
       </c>
       <c r="R59" t="n">
-        <v>6818918</v>
+        <v>6818822</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6330,45 +6321,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125988871</v>
+        <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>98375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488271</v>
+        <v>488244</v>
       </c>
       <c r="R60" t="n">
-        <v>6818822</v>
+        <v>6819028</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125989085</v>
+        <v>125988445</v>
       </c>
       <c r="B61" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488202</v>
+        <v>488400</v>
       </c>
       <c r="R61" t="n">
-        <v>6818963</v>
+        <v>6818592</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125988445</v>
+        <v>125987243</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488400</v>
+        <v>488354</v>
       </c>
       <c r="R62" t="n">
-        <v>6818592</v>
+        <v>6818765</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125987243</v>
+        <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488354</v>
+        <v>488202</v>
       </c>
       <c r="R63" t="n">
-        <v>6818765</v>
+        <v>6818963</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125988482</v>
+        <v>125986843</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,37 +7214,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488376</v>
+        <v>488440</v>
       </c>
       <c r="R69" t="n">
-        <v>6818620</v>
+        <v>6818890</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,12 +7288,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125986843</v>
+        <v>125988482</v>
       </c>
       <c r="B71" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,37 +7408,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488440</v>
+        <v>488376</v>
       </c>
       <c r="R71" t="n">
-        <v>6818890</v>
+        <v>6818620</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7482,12 +7482,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936665</v>
+        <v>125937533</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488458</v>
+        <v>488556</v>
       </c>
       <c r="R4" t="n">
-        <v>6818635</v>
+        <v>6818975</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125937533</v>
+        <v>125937741</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -997,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488556</v>
+        <v>488731</v>
       </c>
       <c r="R5" t="n">
-        <v>6818975</v>
+        <v>6818925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,19 +1051,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937741</v>
+        <v>125936168</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1094,17 +1094,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488731</v>
+        <v>488761</v>
       </c>
       <c r="R6" t="n">
-        <v>6818925</v>
+        <v>6818718</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125935502</v>
+        <v>125936665</v>
       </c>
       <c r="B7" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488799</v>
+        <v>488458</v>
       </c>
       <c r="R7" t="n">
-        <v>6818778</v>
+        <v>6818635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936168</v>
+        <v>125934921</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488761</v>
+        <v>488878</v>
       </c>
       <c r="R8" t="n">
-        <v>6818718</v>
+        <v>6818893</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937321</v>
+        <v>125935502</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488500</v>
+        <v>488799</v>
       </c>
       <c r="R9" t="n">
-        <v>6818934</v>
+        <v>6818778</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125934921</v>
+        <v>125935570</v>
       </c>
       <c r="B10" t="n">
         <v>78732</v>
@@ -1482,17 +1482,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488878</v>
+        <v>488824</v>
       </c>
       <c r="R10" t="n">
-        <v>6818893</v>
+        <v>6818805</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936684</v>
+        <v>125937321</v>
       </c>
       <c r="B11" t="n">
         <v>78732</v>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488631</v>
+        <v>488500</v>
       </c>
       <c r="R11" t="n">
-        <v>6818621</v>
+        <v>6818934</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,19 +1633,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125935570</v>
+        <v>125936684</v>
       </c>
       <c r="B12" t="n">
         <v>78732</v>
@@ -1676,17 +1676,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488824</v>
+        <v>488631</v>
       </c>
       <c r="R12" t="n">
-        <v>6818805</v>
+        <v>6818621</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125934507</v>
+        <v>125937897</v>
       </c>
       <c r="B15" t="n">
-        <v>92524</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488909</v>
+        <v>488805</v>
       </c>
       <c r="R15" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2021,54 +2026,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125935510</v>
+        <v>125934507</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488703</v>
+        <v>488909</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2118,22 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125937897</v>
+        <v>125935510</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2170,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488805</v>
+        <v>488703</v>
       </c>
       <c r="R17" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125937715</v>
+        <v>125934949</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488709</v>
+        <v>488893</v>
       </c>
       <c r="R24" t="n">
-        <v>6818925</v>
+        <v>6818884</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,19 +2904,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125936468</v>
+        <v>125937715</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488715</v>
+        <v>488709</v>
       </c>
       <c r="R25" t="n">
-        <v>6818694</v>
+        <v>6818925</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125934949</v>
+        <v>125936468</v>
       </c>
       <c r="B26" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488893</v>
+        <v>488715</v>
       </c>
       <c r="R26" t="n">
-        <v>6818884</v>
+        <v>6818694</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3309,45 +3309,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125933869</v>
+        <v>125935403</v>
       </c>
       <c r="B29" t="n">
-        <v>91199</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488880</v>
+        <v>488776</v>
       </c>
       <c r="R29" t="n">
-        <v>6818967</v>
+        <v>6818801</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,48 +3406,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125936438</v>
+        <v>125933869</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>91201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488735</v>
+        <v>488880</v>
       </c>
       <c r="R30" t="n">
-        <v>6818743</v>
+        <v>6818967</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3491,19 +3491,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125935403</v>
+        <v>125936438</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3534,17 +3534,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488776</v>
+        <v>488735</v>
       </c>
       <c r="R31" t="n">
-        <v>6818801</v>
+        <v>6818743</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125934563</v>
+        <v>125935283</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,37 +3611,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488882</v>
+        <v>488789</v>
       </c>
       <c r="R32" t="n">
-        <v>6818866</v>
+        <v>6818951</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,19 +3685,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125933949</v>
+        <v>125934563</v>
       </c>
       <c r="B33" t="n">
         <v>79591</v>
@@ -3728,17 +3728,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488891</v>
+        <v>488882</v>
       </c>
       <c r="R33" t="n">
-        <v>6818946</v>
+        <v>6818866</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,22 +3782,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125935283</v>
+        <v>125933949</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488789</v>
+        <v>488891</v>
       </c>
       <c r="R34" t="n">
-        <v>6818951</v>
+        <v>6818946</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R41" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R42" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125934928</v>
+        <v>125936488</v>
       </c>
       <c r="B44" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488878</v>
+        <v>488717</v>
       </c>
       <c r="R44" t="n">
-        <v>6818892</v>
+        <v>6818649</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4854,12 +4854,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125936488</v>
+        <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488717</v>
+        <v>488878</v>
       </c>
       <c r="R46" t="n">
-        <v>6818649</v>
+        <v>6818892</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R54" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R55" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125989221</v>
+        <v>125988482</v>
       </c>
       <c r="B70" t="n">
         <v>78973</v>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488211</v>
+        <v>488376</v>
       </c>
       <c r="R70" t="n">
-        <v>6818972</v>
+        <v>6818620</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,19 +7385,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125988482</v>
+        <v>125989221</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7428,17 +7428,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488376</v>
+        <v>488211</v>
       </c>
       <c r="R71" t="n">
-        <v>6818620</v>
+        <v>6818972</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7482,12 +7482,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125937533</v>
+        <v>125935502</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488556</v>
+        <v>488799</v>
       </c>
       <c r="R4" t="n">
-        <v>6818975</v>
+        <v>6818778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125937741</v>
+        <v>125935570</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488731</v>
+        <v>488824</v>
       </c>
       <c r="R5" t="n">
-        <v>6818925</v>
+        <v>6818805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125936168</v>
+        <v>125937321</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488761</v>
+        <v>488500</v>
       </c>
       <c r="R6" t="n">
-        <v>6818718</v>
+        <v>6818934</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125936665</v>
+        <v>125934921</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488458</v>
+        <v>488878</v>
       </c>
       <c r="R7" t="n">
-        <v>6818635</v>
+        <v>6818893</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125934921</v>
+        <v>125936684</v>
       </c>
       <c r="B8" t="n">
         <v>78732</v>
@@ -1288,17 +1288,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488878</v>
+        <v>488631</v>
       </c>
       <c r="R8" t="n">
-        <v>6818893</v>
+        <v>6818621</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125935502</v>
+        <v>125937533</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488799</v>
+        <v>488556</v>
       </c>
       <c r="R9" t="n">
-        <v>6818778</v>
+        <v>6818975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125935570</v>
+        <v>125937741</v>
       </c>
       <c r="B10" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488824</v>
+        <v>488731</v>
       </c>
       <c r="R10" t="n">
-        <v>6818805</v>
+        <v>6818925</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125937321</v>
+        <v>125936168</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488500</v>
+        <v>488761</v>
       </c>
       <c r="R11" t="n">
-        <v>6818934</v>
+        <v>6818718</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936684</v>
+        <v>125936665</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488631</v>
+        <v>488458</v>
       </c>
       <c r="R12" t="n">
-        <v>6818621</v>
+        <v>6818635</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125937098</v>
+        <v>125937037</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>78640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488445</v>
+        <v>488431</v>
       </c>
       <c r="R27" t="n">
-        <v>6818739</v>
+        <v>6818719</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3181,11 +3181,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3200,22 +3195,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125937037</v>
+        <v>125937098</v>
       </c>
       <c r="B28" t="n">
-        <v>78640</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3223,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3247,13 +3242,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488431</v>
+        <v>488445</v>
       </c>
       <c r="R28" t="n">
-        <v>6818719</v>
+        <v>6818739</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3283,6 +3278,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3297,12 +3297,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R2" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R3" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125935502</v>
+        <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>79591</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488799</v>
+        <v>488458</v>
       </c>
       <c r="R4" t="n">
-        <v>6818778</v>
+        <v>6818635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125935570</v>
+        <v>125936168</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488824</v>
+        <v>488761</v>
       </c>
       <c r="R5" t="n">
-        <v>6818805</v>
+        <v>6818718</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937321</v>
+        <v>125937533</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488500</v>
+        <v>488556</v>
       </c>
       <c r="R6" t="n">
-        <v>6818934</v>
+        <v>6818975</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125934921</v>
+        <v>125937741</v>
       </c>
       <c r="B7" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488878</v>
+        <v>488731</v>
       </c>
       <c r="R7" t="n">
-        <v>6818893</v>
+        <v>6818925</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936684</v>
+        <v>125935502</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488631</v>
+        <v>488799</v>
       </c>
       <c r="R8" t="n">
-        <v>6818621</v>
+        <v>6818778</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937533</v>
+        <v>125935570</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488556</v>
+        <v>488824</v>
       </c>
       <c r="R9" t="n">
-        <v>6818975</v>
+        <v>6818805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125937741</v>
+        <v>125937321</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488731</v>
+        <v>488500</v>
       </c>
       <c r="R10" t="n">
-        <v>6818925</v>
+        <v>6818934</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936168</v>
+        <v>125934921</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488761</v>
+        <v>488878</v>
       </c>
       <c r="R11" t="n">
-        <v>6818718</v>
+        <v>6818893</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936665</v>
+        <v>125936684</v>
       </c>
       <c r="B12" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488458</v>
+        <v>488631</v>
       </c>
       <c r="R12" t="n">
-        <v>6818635</v>
+        <v>6818621</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,22 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B13" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R13" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R14" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,60 +1924,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>92528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R15" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2026,54 +2021,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2123,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125935014</v>
+        <v>125937715</v>
       </c>
       <c r="B23" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488848</v>
+        <v>488709</v>
       </c>
       <c r="R23" t="n">
-        <v>6818924</v>
+        <v>6818925</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125934949</v>
+        <v>125935014</v>
       </c>
       <c r="B24" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488893</v>
+        <v>488848</v>
       </c>
       <c r="R24" t="n">
-        <v>6818884</v>
+        <v>6818924</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125937715</v>
+        <v>125936468</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488709</v>
+        <v>488715</v>
       </c>
       <c r="R25" t="n">
-        <v>6818925</v>
+        <v>6818694</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125936468</v>
+        <v>125934949</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488715</v>
+        <v>488893</v>
       </c>
       <c r="R26" t="n">
-        <v>6818694</v>
+        <v>6818884</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3409,7 +3409,7 @@
         <v>125933869</v>
       </c>
       <c r="B30" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125935283</v>
+        <v>125933949</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488789</v>
+        <v>488891</v>
       </c>
       <c r="R32" t="n">
-        <v>6818951</v>
+        <v>6818946</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125934563</v>
+        <v>125935283</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488882</v>
+        <v>488789</v>
       </c>
       <c r="R33" t="n">
-        <v>6818866</v>
+        <v>6818951</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,19 +3782,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125933949</v>
+        <v>125934563</v>
       </c>
       <c r="B34" t="n">
         <v>79591</v>
@@ -3825,17 +3825,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488891</v>
+        <v>488882</v>
       </c>
       <c r="R34" t="n">
-        <v>6818946</v>
+        <v>6818866</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3879,12 +3879,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R36" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B37" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R37" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B38" t="n">
-        <v>78640</v>
+        <v>91203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R38" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B39" t="n">
-        <v>91201</v>
+        <v>78640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R39" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125934928</v>
+        <v>125932852</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488878</v>
+        <v>488802</v>
       </c>
       <c r="R46" t="n">
-        <v>6818892</v>
+        <v>6819049</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125932852</v>
+        <v>125934928</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488802</v>
+        <v>488878</v>
       </c>
       <c r="R47" t="n">
-        <v>6819049</v>
+        <v>6818892</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5145,12 +5145,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R50" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R51" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B54" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R54" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R55" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125988445</v>
+        <v>125989085</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488400</v>
+        <v>488202</v>
       </c>
       <c r="R61" t="n">
-        <v>6818592</v>
+        <v>6818963</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125987243</v>
+        <v>125988445</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488354</v>
+        <v>488400</v>
       </c>
       <c r="R62" t="n">
-        <v>6818765</v>
+        <v>6818592</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R63" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7979,10 +7979,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125985190</v>
+        <v>125987019</v>
       </c>
       <c r="B77" t="n">
-        <v>78731</v>
+        <v>57812</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488327</v>
+        <v>488514</v>
       </c>
       <c r="R77" t="n">
-        <v>6818968</v>
+        <v>6818802</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R78" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125987019</v>
+        <v>125983993</v>
       </c>
       <c r="B79" t="n">
-        <v>57812</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488514</v>
+        <v>488175</v>
       </c>
       <c r="R79" t="n">
-        <v>6818802</v>
+        <v>6819105</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8270,45 +8270,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125987994</v>
+        <v>125989375</v>
       </c>
       <c r="B80" t="n">
-        <v>78731</v>
+        <v>98379</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488450</v>
+        <v>488248</v>
       </c>
       <c r="R80" t="n">
-        <v>6818611</v>
+        <v>6819009</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8367,10 +8376,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125989375</v>
+        <v>125984338</v>
       </c>
       <c r="B81" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8397,7 +8406,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8411,10 +8420,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488248</v>
+        <v>488234</v>
       </c>
       <c r="R81" t="n">
-        <v>6819009</v>
+        <v>6819040</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8473,54 +8482,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125984338</v>
+        <v>125987994</v>
       </c>
       <c r="B82" t="n">
-        <v>98377</v>
+        <v>78731</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488234</v>
+        <v>488450</v>
       </c>
       <c r="R82" t="n">
-        <v>6819040</v>
+        <v>6818611</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R2" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R3" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R18" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,13 +2369,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R19" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125933949</v>
+        <v>125935283</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488891</v>
+        <v>488789</v>
       </c>
       <c r="R32" t="n">
-        <v>6818946</v>
+        <v>6818951</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125935283</v>
+        <v>125934563</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,37 +3708,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488789</v>
+        <v>488882</v>
       </c>
       <c r="R33" t="n">
-        <v>6818951</v>
+        <v>6818866</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,19 +3782,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125934563</v>
+        <v>125933949</v>
       </c>
       <c r="B34" t="n">
         <v>79591</v>
@@ -3825,17 +3825,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488882</v>
+        <v>488891</v>
       </c>
       <c r="R34" t="n">
-        <v>6818866</v>
+        <v>6818946</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3879,12 +3879,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R41" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125934399</v>
+        <v>125935887</v>
       </c>
       <c r="B42" t="n">
-        <v>79591</v>
+        <v>57652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488895</v>
+        <v>488851</v>
       </c>
       <c r="R42" t="n">
-        <v>6818859</v>
+        <v>6818708</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4641,6 +4641,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4667,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125935887</v>
+        <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488851</v>
+        <v>488845</v>
       </c>
       <c r="R43" t="n">
-        <v>6818708</v>
+        <v>6818675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4738,11 +4743,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R50" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R51" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -8270,54 +8270,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125989375</v>
+        <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>98379</v>
+        <v>78731</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488248</v>
+        <v>488450</v>
       </c>
       <c r="R80" t="n">
-        <v>6819009</v>
+        <v>6818611</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8376,7 +8367,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125984338</v>
+        <v>125989375</v>
       </c>
       <c r="B81" t="n">
         <v>98379</v>
@@ -8406,7 +8397,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8420,10 +8411,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488234</v>
+        <v>488248</v>
       </c>
       <c r="R81" t="n">
-        <v>6819040</v>
+        <v>6819009</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8482,45 +8473,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125987994</v>
+        <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>78731</v>
+        <v>98379</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488450</v>
+        <v>488234</v>
       </c>
       <c r="R82" t="n">
-        <v>6818611</v>
+        <v>6819040</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R2" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R3" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936665</v>
+        <v>125937321</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488458</v>
+        <v>488500</v>
       </c>
       <c r="R4" t="n">
-        <v>6818635</v>
+        <v>6818934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125936168</v>
+        <v>125936684</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488761</v>
+        <v>488631</v>
       </c>
       <c r="R5" t="n">
-        <v>6818718</v>
+        <v>6818621</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937533</v>
+        <v>125935570</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488556</v>
+        <v>488824</v>
       </c>
       <c r="R6" t="n">
-        <v>6818975</v>
+        <v>6818805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125937741</v>
+        <v>125934921</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488731</v>
+        <v>488878</v>
       </c>
       <c r="R7" t="n">
-        <v>6818925</v>
+        <v>6818893</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125935502</v>
+        <v>125936665</v>
       </c>
       <c r="B8" t="n">
-        <v>79591</v>
+        <v>78735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488799</v>
+        <v>488458</v>
       </c>
       <c r="R8" t="n">
-        <v>6818778</v>
+        <v>6818635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125935570</v>
+        <v>125937533</v>
       </c>
       <c r="B9" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488824</v>
+        <v>488556</v>
       </c>
       <c r="R9" t="n">
-        <v>6818805</v>
+        <v>6818975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125937321</v>
+        <v>125937741</v>
       </c>
       <c r="B10" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488500</v>
+        <v>488731</v>
       </c>
       <c r="R10" t="n">
-        <v>6818934</v>
+        <v>6818925</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125934921</v>
+        <v>125935502</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488878</v>
+        <v>488799</v>
       </c>
       <c r="R11" t="n">
-        <v>6818893</v>
+        <v>6818778</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936684</v>
+        <v>125936168</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488631</v>
+        <v>488761</v>
       </c>
       <c r="R12" t="n">
-        <v>6818621</v>
+        <v>6818718</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1745,7 +1745,7 @@
         <v>125934762</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125934407</v>
       </c>
       <c r="B14" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125934507</v>
+        <v>125937897</v>
       </c>
       <c r="B15" t="n">
-        <v>92528</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488909</v>
+        <v>488805</v>
       </c>
       <c r="R15" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2021,54 +2026,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125935510</v>
+        <v>125934507</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488703</v>
+        <v>488909</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2118,22 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125937897</v>
+        <v>125935510</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,13 +2170,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488805</v>
+        <v>488703</v>
       </c>
       <c r="R17" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R18" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,13 +2364,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R19" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2434,7 +2434,7 @@
         <v>125935224</v>
       </c>
       <c r="B20" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125933626</v>
       </c>
       <c r="B21" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125932883</v>
       </c>
       <c r="B22" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125937715</v>
+        <v>125934949</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488709</v>
+        <v>488893</v>
       </c>
       <c r="R23" t="n">
-        <v>6818925</v>
+        <v>6818884</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
         <v>125935014</v>
       </c>
       <c r="B24" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125936468</v>
+        <v>125937715</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488715</v>
+        <v>488709</v>
       </c>
       <c r="R25" t="n">
-        <v>6818694</v>
+        <v>6818925</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125934949</v>
+        <v>125936468</v>
       </c>
       <c r="B26" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488893</v>
+        <v>488715</v>
       </c>
       <c r="R26" t="n">
-        <v>6818884</v>
+        <v>6818694</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
         <v>125937037</v>
       </c>
       <c r="B27" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>125937098</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3309,45 +3309,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125935403</v>
+        <v>125933869</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>91207</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488776</v>
+        <v>488880</v>
       </c>
       <c r="R29" t="n">
-        <v>6818801</v>
+        <v>6818967</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,48 +3406,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125933869</v>
+        <v>125936438</v>
       </c>
       <c r="B30" t="n">
-        <v>91203</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488880</v>
+        <v>488735</v>
       </c>
       <c r="R30" t="n">
-        <v>6818967</v>
+        <v>6818743</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3491,22 +3491,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125936438</v>
+        <v>125935403</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,17 +3534,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488735</v>
+        <v>488776</v>
       </c>
       <c r="R31" t="n">
-        <v>6818743</v>
+        <v>6818801</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125935283</v>
+        <v>125934563</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,37 +3611,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488789</v>
+        <v>488882</v>
       </c>
       <c r="R32" t="n">
-        <v>6818951</v>
+        <v>6818866</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,22 +3685,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125934563</v>
+        <v>125933949</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,17 +3728,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488882</v>
+        <v>488891</v>
       </c>
       <c r="R33" t="n">
-        <v>6818866</v>
+        <v>6818946</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3782,22 +3782,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125933949</v>
+        <v>125935283</v>
       </c>
       <c r="B34" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488891</v>
+        <v>488789</v>
       </c>
       <c r="R34" t="n">
-        <v>6818946</v>
+        <v>6818951</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125936448</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B36" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R36" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R37" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B38" t="n">
-        <v>91203</v>
+        <v>78644</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R38" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>78640</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R39" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>125935537</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125935887</v>
+        <v>125936025</v>
       </c>
       <c r="B42" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488851</v>
+        <v>488845</v>
       </c>
       <c r="R42" t="n">
-        <v>6818708</v>
+        <v>6818675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4641,11 +4641,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4672,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125936025</v>
+        <v>125935887</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,34 +4678,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488845</v>
+        <v>488851</v>
       </c>
       <c r="R43" t="n">
-        <v>6818675</v>
+        <v>6818708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4743,6 +4738,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125936488</v>
+        <v>125936447</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488717</v>
+        <v>488656</v>
       </c>
       <c r="R44" t="n">
-        <v>6818649</v>
+        <v>6818762</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936447</v>
+        <v>125936488</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488656</v>
+        <v>488717</v>
       </c>
       <c r="R45" t="n">
-        <v>6818762</v>
+        <v>6818649</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125932852</v>
+        <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488802</v>
+        <v>488878</v>
       </c>
       <c r="R46" t="n">
-        <v>6819049</v>
+        <v>6818892</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,22 +5048,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125934928</v>
+        <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488878</v>
+        <v>488802</v>
       </c>
       <c r="R47" t="n">
-        <v>6818892</v>
+        <v>6819049</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5145,22 +5145,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R48" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B49" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R49" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5354,7 +5354,7 @@
         <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125984809</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R54" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R55" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>125986685</v>
       </c>
       <c r="B56" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125988566</v>
       </c>
       <c r="B57" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125986131</v>
+        <v>125988871</v>
       </c>
       <c r="B58" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6138,34 +6138,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488444</v>
+        <v>488271</v>
       </c>
       <c r="R58" t="n">
-        <v>6818918</v>
+        <v>6818822</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125988871</v>
+        <v>125986131</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488271</v>
+        <v>488444</v>
       </c>
       <c r="R59" t="n">
-        <v>6818822</v>
+        <v>6818918</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6324,7 +6324,7 @@
         <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B61" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,21 +6438,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6462,13 +6462,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R61" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>125988445</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125987243</v>
+        <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488354</v>
+        <v>488202</v>
       </c>
       <c r="R63" t="n">
-        <v>6818765</v>
+        <v>6818963</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>125984038</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>125988735</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>125984150</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>125988835</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125986843</v>
+        <v>125988482</v>
       </c>
       <c r="B69" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,37 +7214,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488440</v>
+        <v>488376</v>
       </c>
       <c r="R69" t="n">
-        <v>6818890</v>
+        <v>6818620</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,22 +7288,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125988482</v>
+        <v>125989221</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488376</v>
+        <v>488211</v>
       </c>
       <c r="R70" t="n">
-        <v>6818620</v>
+        <v>6818972</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,22 +7385,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125989221</v>
+        <v>125986843</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488211</v>
+        <v>488440</v>
       </c>
       <c r="R71" t="n">
-        <v>6818972</v>
+        <v>6818890</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>125985280</v>
       </c>
       <c r="B73" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>125985181</v>
       </c>
       <c r="B74" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>125986283</v>
       </c>
       <c r="B75" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>125987019</v>
       </c>
       <c r="B77" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125985190</v>
+        <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78731</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488327</v>
+        <v>488175</v>
       </c>
       <c r="R78" t="n">
-        <v>6818968</v>
+        <v>6819105</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78735</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,21 +8184,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8208,13 +8208,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R79" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8258,12 +8258,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
         <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>125988725</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R2" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R3" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1936,48 +1936,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R15" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2026,54 +2021,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2123,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125934949</v>
+        <v>125935014</v>
       </c>
       <c r="B23" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488893</v>
+        <v>488848</v>
       </c>
       <c r="R23" t="n">
-        <v>6818884</v>
+        <v>6818924</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125935014</v>
+        <v>125937715</v>
       </c>
       <c r="B24" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488848</v>
+        <v>488709</v>
       </c>
       <c r="R24" t="n">
-        <v>6818924</v>
+        <v>6818925</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,19 +2904,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125937715</v>
+        <v>125936468</v>
       </c>
       <c r="B25" t="n">
         <v>78977</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488709</v>
+        <v>488715</v>
       </c>
       <c r="R25" t="n">
-        <v>6818925</v>
+        <v>6818694</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125936468</v>
+        <v>125934949</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488715</v>
+        <v>488893</v>
       </c>
       <c r="R26" t="n">
-        <v>6818694</v>
+        <v>6818884</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R48" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R49" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6427,7 +6427,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125987243</v>
+        <v>125988445</v>
       </c>
       <c r="B61" t="n">
         <v>78977</v>
@@ -6458,17 +6458,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488354</v>
+        <v>488400</v>
       </c>
       <c r="R61" t="n">
-        <v>6818765</v>
+        <v>6818592</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,22 +6512,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125988445</v>
+        <v>125989085</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488400</v>
+        <v>488202</v>
       </c>
       <c r="R62" t="n">
-        <v>6818592</v>
+        <v>6818963</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R63" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988605</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488257</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
-        <v>6818880</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985280</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
         <v>78736</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488376</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
         <v>78736</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125986283</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
         <v>78736</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488483</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988576</v>
+        <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488336</v>
+        <v>488257</v>
       </c>
       <c r="R76" t="n">
-        <v>6818701</v>
+        <v>6818880</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125987019</v>
+        <v>125983993</v>
       </c>
       <c r="B77" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,34 +7990,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488514</v>
+        <v>488175</v>
       </c>
       <c r="R77" t="n">
-        <v>6818802</v>
+        <v>6819105</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R78" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125985190</v>
+        <v>125987019</v>
       </c>
       <c r="B79" t="n">
-        <v>78735</v>
+        <v>57816</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,37 +8184,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488327</v>
+        <v>488514</v>
       </c>
       <c r="R79" t="n">
-        <v>6818968</v>
+        <v>6818802</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8258,12 +8258,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125937321</v>
+        <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488500</v>
+        <v>488458</v>
       </c>
       <c r="R4" t="n">
-        <v>6818934</v>
+        <v>6818635</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125936684</v>
+        <v>125937533</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488631</v>
+        <v>488556</v>
       </c>
       <c r="R5" t="n">
-        <v>6818621</v>
+        <v>6818975</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125935570</v>
+        <v>125937741</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488824</v>
+        <v>488731</v>
       </c>
       <c r="R6" t="n">
-        <v>6818805</v>
+        <v>6818925</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125934921</v>
+        <v>125935502</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488878</v>
+        <v>488799</v>
       </c>
       <c r="R7" t="n">
-        <v>6818893</v>
+        <v>6818778</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936665</v>
+        <v>125936168</v>
       </c>
       <c r="B8" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488458</v>
+        <v>488761</v>
       </c>
       <c r="R8" t="n">
-        <v>6818635</v>
+        <v>6818718</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937533</v>
+        <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488556</v>
+        <v>488500</v>
       </c>
       <c r="R9" t="n">
-        <v>6818975</v>
+        <v>6818934</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125937741</v>
+        <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488731</v>
+        <v>488878</v>
       </c>
       <c r="R10" t="n">
-        <v>6818925</v>
+        <v>6818893</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125935502</v>
+        <v>125936684</v>
       </c>
       <c r="B11" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488799</v>
+        <v>488631</v>
       </c>
       <c r="R11" t="n">
-        <v>6818778</v>
+        <v>6818621</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936168</v>
+        <v>125935570</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488761</v>
+        <v>488824</v>
       </c>
       <c r="R12" t="n">
-        <v>6818718</v>
+        <v>6818805</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R13" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B14" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R14" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125988871</v>
+        <v>125986131</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6138,34 +6138,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488271</v>
+        <v>488444</v>
       </c>
       <c r="R58" t="n">
-        <v>6818822</v>
+        <v>6818918</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125986131</v>
+        <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6235,34 +6235,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488444</v>
+        <v>488271</v>
       </c>
       <c r="R59" t="n">
-        <v>6818918</v>
+        <v>6818822</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6324,7 +6324,7 @@
         <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B62" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6535,21 +6535,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6559,13 +6559,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R62" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6621,10 +6621,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125987243</v>
+        <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488354</v>
+        <v>488202</v>
       </c>
       <c r="R63" t="n">
-        <v>6818765</v>
+        <v>6818963</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6815,48 +6815,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125986119</v>
+        <v>125988735</v>
       </c>
       <c r="B65" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488459</v>
+        <v>488266</v>
       </c>
       <c r="R65" t="n">
-        <v>6818981</v>
+        <v>6818782</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6900,60 +6900,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125988735</v>
+        <v>125986119</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488266</v>
+        <v>488459</v>
       </c>
       <c r="R66" t="n">
-        <v>6818782</v>
+        <v>6818981</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6997,12 +6997,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488257</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818880</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
         <v>78736</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
         <v>78736</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
         <v>78736</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988605</v>
+        <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488257</v>
+        <v>488336</v>
       </c>
       <c r="R76" t="n">
-        <v>6818880</v>
+        <v>6818701</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,21 +7990,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8014,13 +8014,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R77" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125985190</v>
+        <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488327</v>
+        <v>488175</v>
       </c>
       <c r="R78" t="n">
-        <v>6818968</v>
+        <v>6819105</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,12 +8161,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936665</v>
+        <v>125937321</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488458</v>
+        <v>488500</v>
       </c>
       <c r="R4" t="n">
-        <v>6818635</v>
+        <v>6818934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125937533</v>
+        <v>125934921</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488556</v>
+        <v>488878</v>
       </c>
       <c r="R5" t="n">
-        <v>6818975</v>
+        <v>6818893</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937741</v>
+        <v>125936684</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488731</v>
+        <v>488631</v>
       </c>
       <c r="R6" t="n">
-        <v>6818925</v>
+        <v>6818621</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125935502</v>
+        <v>125935570</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488799</v>
+        <v>488824</v>
       </c>
       <c r="R7" t="n">
-        <v>6818778</v>
+        <v>6818805</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936168</v>
+        <v>125936665</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488761</v>
+        <v>488458</v>
       </c>
       <c r="R8" t="n">
-        <v>6818718</v>
+        <v>6818635</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937321</v>
+        <v>125937533</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488500</v>
+        <v>488556</v>
       </c>
       <c r="R9" t="n">
-        <v>6818934</v>
+        <v>6818975</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125934921</v>
+        <v>125937741</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488878</v>
+        <v>488731</v>
       </c>
       <c r="R10" t="n">
-        <v>6818893</v>
+        <v>6818925</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936684</v>
+        <v>125935502</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488631</v>
+        <v>488799</v>
       </c>
       <c r="R11" t="n">
-        <v>6818621</v>
+        <v>6818778</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125935570</v>
+        <v>125936168</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488824</v>
+        <v>488761</v>
       </c>
       <c r="R12" t="n">
-        <v>6818805</v>
+        <v>6818718</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R36" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B37" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R37" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125937321</v>
+        <v>125936168</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488500</v>
+        <v>488761</v>
       </c>
       <c r="R4" t="n">
-        <v>6818934</v>
+        <v>6818718</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125934921</v>
+        <v>125936665</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488878</v>
+        <v>488458</v>
       </c>
       <c r="R5" t="n">
-        <v>6818893</v>
+        <v>6818635</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125936684</v>
+        <v>125937533</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488631</v>
+        <v>488556</v>
       </c>
       <c r="R6" t="n">
-        <v>6818621</v>
+        <v>6818975</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125935570</v>
+        <v>125937741</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488824</v>
+        <v>488731</v>
       </c>
       <c r="R7" t="n">
-        <v>6818805</v>
+        <v>6818925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936665</v>
+        <v>125935502</v>
       </c>
       <c r="B8" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488458</v>
+        <v>488799</v>
       </c>
       <c r="R8" t="n">
-        <v>6818635</v>
+        <v>6818778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937533</v>
+        <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488556</v>
+        <v>488500</v>
       </c>
       <c r="R9" t="n">
-        <v>6818975</v>
+        <v>6818934</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125937741</v>
+        <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488731</v>
+        <v>488878</v>
       </c>
       <c r="R10" t="n">
-        <v>6818925</v>
+        <v>6818893</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125935502</v>
+        <v>125936684</v>
       </c>
       <c r="B11" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488799</v>
+        <v>488631</v>
       </c>
       <c r="R11" t="n">
-        <v>6818778</v>
+        <v>6818621</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125936168</v>
+        <v>125935570</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488761</v>
+        <v>488824</v>
       </c>
       <c r="R12" t="n">
-        <v>6818718</v>
+        <v>6818805</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B13" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R13" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R14" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,54 +1924,54 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B15" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R15" t="n">
         <v>6818877</v>
@@ -2021,22 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R16" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2104,6 +2104,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,48 +2135,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>92532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R17" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2220,12 +2220,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125935014</v>
+        <v>125937715</v>
       </c>
       <c r="B23" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488848</v>
+        <v>488709</v>
       </c>
       <c r="R23" t="n">
-        <v>6818924</v>
+        <v>6818925</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125937715</v>
+        <v>125935014</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488709</v>
+        <v>488848</v>
       </c>
       <c r="R24" t="n">
-        <v>6818925</v>
+        <v>6818924</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,12 +2904,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125936438</v>
+        <v>125935403</v>
       </c>
       <c r="B30" t="n">
         <v>78977</v>
@@ -3437,17 +3437,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488735</v>
+        <v>488776</v>
       </c>
       <c r="R30" t="n">
-        <v>6818743</v>
+        <v>6818801</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3491,19 +3491,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125935403</v>
+        <v>125936438</v>
       </c>
       <c r="B31" t="n">
         <v>78977</v>
@@ -3534,17 +3534,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488776</v>
+        <v>488735</v>
       </c>
       <c r="R31" t="n">
-        <v>6818801</v>
+        <v>6818743</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3588,19 +3588,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125934563</v>
+        <v>125933949</v>
       </c>
       <c r="B32" t="n">
         <v>79595</v>
@@ -3631,17 +3631,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488882</v>
+        <v>488891</v>
       </c>
       <c r="R32" t="n">
-        <v>6818866</v>
+        <v>6818946</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,22 +3685,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125933949</v>
+        <v>125935283</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488891</v>
+        <v>488789</v>
       </c>
       <c r="R33" t="n">
-        <v>6818946</v>
+        <v>6818951</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125935283</v>
+        <v>125934563</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,37 +3805,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488789</v>
+        <v>488882</v>
       </c>
       <c r="R34" t="n">
-        <v>6818951</v>
+        <v>6818866</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3879,12 +3879,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B38" t="n">
-        <v>78644</v>
+        <v>91207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R38" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>78644</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R39" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125934399</v>
+        <v>125935887</v>
       </c>
       <c r="B41" t="n">
-        <v>79595</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488895</v>
+        <v>488851</v>
       </c>
       <c r="R41" t="n">
-        <v>6818859</v>
+        <v>6818708</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4570,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4586,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R42" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125935887</v>
+        <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488851</v>
+        <v>488845</v>
       </c>
       <c r="R43" t="n">
-        <v>6818708</v>
+        <v>6818675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4738,11 +4743,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125936447</v>
+        <v>125936488</v>
       </c>
       <c r="B44" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488656</v>
+        <v>488717</v>
       </c>
       <c r="R44" t="n">
-        <v>6818762</v>
+        <v>6818649</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936488</v>
+        <v>125936447</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488717</v>
+        <v>488656</v>
       </c>
       <c r="R45" t="n">
-        <v>6818649</v>
+        <v>6818762</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,12 +4951,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6815,48 +6815,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125988735</v>
+        <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488266</v>
+        <v>488459</v>
       </c>
       <c r="R65" t="n">
-        <v>6818782</v>
+        <v>6818981</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6900,60 +6900,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125986119</v>
+        <v>125988735</v>
       </c>
       <c r="B66" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488459</v>
+        <v>488266</v>
       </c>
       <c r="R66" t="n">
-        <v>6818981</v>
+        <v>6818782</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6997,12 +6997,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988605</v>
+        <v>125986283</v>
       </c>
       <c r="B72" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488257</v>
+        <v>488483</v>
       </c>
       <c r="R72" t="n">
-        <v>6818880</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985280</v>
+        <v>125988576</v>
       </c>
       <c r="B73" t="n">
         <v>78736</v>
@@ -7622,14 +7622,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488376</v>
+        <v>488336</v>
       </c>
       <c r="R73" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B74" t="n">
         <v>78736</v>
@@ -7723,10 +7723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7785,7 +7785,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B75" t="n">
         <v>78736</v>
@@ -7820,13 +7820,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988576</v>
+        <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488336</v>
+        <v>488257</v>
       </c>
       <c r="R76" t="n">
-        <v>6818701</v>
+        <v>6818880</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,12 +7967,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936168</v>
+        <v>125936665</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488761</v>
+        <v>488458</v>
       </c>
       <c r="R4" t="n">
-        <v>6818718</v>
+        <v>6818635</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125936665</v>
+        <v>125936168</v>
       </c>
       <c r="B5" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488458</v>
+        <v>488761</v>
       </c>
       <c r="R5" t="n">
-        <v>6818635</v>
+        <v>6818718</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B38" t="n">
-        <v>91207</v>
+        <v>78644</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R38" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>78644</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R39" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R2" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R3" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936665</v>
+        <v>125935502</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488458</v>
+        <v>488799</v>
       </c>
       <c r="R4" t="n">
-        <v>6818635</v>
+        <v>6818778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125936168</v>
+        <v>125936665</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488761</v>
+        <v>488458</v>
       </c>
       <c r="R5" t="n">
-        <v>6818718</v>
+        <v>6818635</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125937533</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125937741</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125935502</v>
+        <v>125936168</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488799</v>
+        <v>488761</v>
       </c>
       <c r="R8" t="n">
-        <v>6818778</v>
+        <v>6818718</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125936684</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125935570</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R13" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B14" t="n">
-        <v>78644</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R14" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R15" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,6 +2007,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,48 +2038,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>92535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R16" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2104,11 +2109,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2123,54 +2123,54 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B17" t="n">
-        <v>92532</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R17" t="n">
         <v>6818877</v>
@@ -2220,22 +2220,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R18" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,13 +2369,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R19" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2400,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2434,7 +2434,7 @@
         <v>125935224</v>
       </c>
       <c r="B20" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>125933626</v>
       </c>
       <c r="B21" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>125932883</v>
       </c>
       <c r="B22" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125937715</v>
+        <v>125934949</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,37 +2733,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488709</v>
+        <v>488893</v>
       </c>
       <c r="R23" t="n">
-        <v>6818925</v>
+        <v>6818884</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2822,7 +2822,7 @@
         <v>125935014</v>
       </c>
       <c r="B24" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125936468</v>
+        <v>125937715</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488715</v>
+        <v>488709</v>
       </c>
       <c r="R25" t="n">
-        <v>6818694</v>
+        <v>6818925</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125934949</v>
+        <v>125936468</v>
       </c>
       <c r="B26" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488893</v>
+        <v>488715</v>
       </c>
       <c r="R26" t="n">
-        <v>6818884</v>
+        <v>6818694</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,22 +3098,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125937037</v>
+        <v>125937098</v>
       </c>
       <c r="B27" t="n">
-        <v>78644</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488431</v>
+        <v>488445</v>
       </c>
       <c r="R27" t="n">
-        <v>6818719</v>
+        <v>6818739</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3181,6 +3181,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3195,22 +3200,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125937098</v>
+        <v>125937037</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>78647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3223,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,13 +3247,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488445</v>
+        <v>488431</v>
       </c>
       <c r="R28" t="n">
-        <v>6818739</v>
+        <v>6818719</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3278,11 +3283,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3297,12 +3297,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
         <v>125933869</v>
       </c>
       <c r="B29" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125935403</v>
+        <v>125936438</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,17 +3437,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488776</v>
+        <v>488735</v>
       </c>
       <c r="R30" t="n">
-        <v>6818801</v>
+        <v>6818743</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3491,22 +3491,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125936438</v>
+        <v>125935403</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,17 +3534,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488735</v>
+        <v>488776</v>
       </c>
       <c r="R31" t="n">
-        <v>6818743</v>
+        <v>6818801</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125933949</v>
+        <v>125935283</v>
       </c>
       <c r="B32" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,21 +3611,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3635,13 +3635,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488891</v>
+        <v>488789</v>
       </c>
       <c r="R32" t="n">
-        <v>6818946</v>
+        <v>6818951</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125935283</v>
+        <v>125933949</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,21 +3708,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488789</v>
+        <v>488891</v>
       </c>
       <c r="R33" t="n">
-        <v>6818951</v>
+        <v>6818946</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>125934563</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>125936448</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B36" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R36" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R37" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B38" t="n">
-        <v>78644</v>
+        <v>91210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R38" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>78647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R39" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>125935537</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>125935887</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125936488</v>
+        <v>125936447</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488717</v>
+        <v>488656</v>
       </c>
       <c r="R44" t="n">
-        <v>6818649</v>
+        <v>6818762</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4854,22 +4854,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936447</v>
+        <v>125934928</v>
       </c>
       <c r="B45" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4897,17 +4897,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488656</v>
+        <v>488878</v>
       </c>
       <c r="R45" t="n">
-        <v>6818762</v>
+        <v>6818892</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125934928</v>
+        <v>125936488</v>
       </c>
       <c r="B46" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488878</v>
+        <v>488717</v>
       </c>
       <c r="R46" t="n">
-        <v>6818892</v>
+        <v>6818649</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5063,7 +5063,7 @@
         <v>125932852</v>
       </c>
       <c r="B47" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R50" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B51" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R51" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>125989251</v>
       </c>
       <c r="B52" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>125984809</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B54" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R54" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R55" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>125986685</v>
       </c>
       <c r="B56" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>125988566</v>
       </c>
       <c r="B57" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6127,45 +6127,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125986131</v>
+        <v>125984440</v>
       </c>
       <c r="B58" t="n">
-        <v>78735</v>
+        <v>98395</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488444</v>
+        <v>488244</v>
       </c>
       <c r="R58" t="n">
-        <v>6818918</v>
+        <v>6819028</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6227,7 +6236,7 @@
         <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6321,54 +6330,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125984440</v>
+        <v>125986131</v>
       </c>
       <c r="B60" t="n">
-        <v>98386</v>
+        <v>78738</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488244</v>
+        <v>488444</v>
       </c>
       <c r="R60" t="n">
-        <v>6819028</v>
+        <v>6818918</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6430,7 +6430,7 @@
         <v>125988445</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>125987243</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>125984038</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>125986119</v>
       </c>
       <c r="B65" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>125988735</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>125984150</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>125988835</v>
       </c>
       <c r="B68" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125988482</v>
+        <v>125986843</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,37 +7214,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488376</v>
+        <v>488440</v>
       </c>
       <c r="R69" t="n">
-        <v>6818620</v>
+        <v>6818890</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,22 +7288,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125989221</v>
+        <v>125988482</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488211</v>
+        <v>488376</v>
       </c>
       <c r="R70" t="n">
-        <v>6818972</v>
+        <v>6818620</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,22 +7385,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125986843</v>
+        <v>125989221</v>
       </c>
       <c r="B71" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488440</v>
+        <v>488211</v>
       </c>
       <c r="R71" t="n">
-        <v>6818890</v>
+        <v>6818972</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125986283</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488483</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
         <v>6818970</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,22 +7579,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125988576</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7622,14 +7622,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488336</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818701</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,10 +7688,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985280</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488376</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
         <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,22 +7773,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125985181</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7816,14 +7816,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488320</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818956</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -7885,7 +7885,7 @@
         <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7979,10 +7979,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125985190</v>
+        <v>125987019</v>
       </c>
       <c r="B77" t="n">
-        <v>78735</v>
+        <v>57817</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488327</v>
+        <v>488514</v>
       </c>
       <c r="R77" t="n">
-        <v>6818968</v>
+        <v>6818802</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125983993</v>
+        <v>125985190</v>
       </c>
       <c r="B78" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488175</v>
+        <v>488327</v>
       </c>
       <c r="R78" t="n">
-        <v>6819105</v>
+        <v>6818968</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125987019</v>
+        <v>125983993</v>
       </c>
       <c r="B79" t="n">
-        <v>57816</v>
+        <v>78980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488514</v>
+        <v>488175</v>
       </c>
       <c r="R79" t="n">
-        <v>6818802</v>
+        <v>6819105</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8273,7 +8273,7 @@
         <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>125989375</v>
       </c>
       <c r="B81" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>125988725</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R13" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>78647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R14" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,12 +1924,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125934949</v>
+        <v>125935014</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488893</v>
+        <v>488848</v>
       </c>
       <c r="R23" t="n">
-        <v>6818884</v>
+        <v>6818924</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125935014</v>
+        <v>125934949</v>
       </c>
       <c r="B24" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488848</v>
+        <v>488893</v>
       </c>
       <c r="R24" t="n">
-        <v>6818924</v>
+        <v>6818884</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R48" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B49" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R49" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988605</v>
       </c>
       <c r="B72" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488257</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818880</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
         <v>78739</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
         <v>78739</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
         <v>78739</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988605</v>
+        <v>125988576</v>
       </c>
       <c r="B76" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488257</v>
+        <v>488336</v>
       </c>
       <c r="R76" t="n">
-        <v>6818880</v>
+        <v>6818701</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,12 +7967,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8270,45 +8270,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125987994</v>
+        <v>125989375</v>
       </c>
       <c r="B80" t="n">
-        <v>78738</v>
+        <v>98395</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488450</v>
+        <v>488248</v>
       </c>
       <c r="R80" t="n">
-        <v>6818611</v>
+        <v>6819009</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8367,7 +8376,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125989375</v>
+        <v>125984338</v>
       </c>
       <c r="B81" t="n">
         <v>98395</v>
@@ -8397,7 +8406,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8411,10 +8420,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488248</v>
+        <v>488234</v>
       </c>
       <c r="R81" t="n">
-        <v>6819009</v>
+        <v>6819040</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8473,54 +8482,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125984338</v>
+        <v>125987994</v>
       </c>
       <c r="B82" t="n">
-        <v>98395</v>
+        <v>78738</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488234</v>
+        <v>488450</v>
       </c>
       <c r="R82" t="n">
-        <v>6819040</v>
+        <v>6818611</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125936622</v>
+        <v>125934616</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488654</v>
+        <v>488839</v>
       </c>
       <c r="R2" t="n">
-        <v>6818633</v>
+        <v>6818918</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125934616</v>
+        <v>125936622</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488839</v>
+        <v>488654</v>
       </c>
       <c r="R3" t="n">
-        <v>6818918</v>
+        <v>6818633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125935502</v>
+        <v>125936684</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488799</v>
+        <v>488631</v>
       </c>
       <c r="R4" t="n">
-        <v>6818778</v>
+        <v>6818621</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125936665</v>
+        <v>125935570</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488458</v>
+        <v>488824</v>
       </c>
       <c r="R5" t="n">
-        <v>6818635</v>
+        <v>6818805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937533</v>
+        <v>125936665</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488556</v>
+        <v>488458</v>
       </c>
       <c r="R6" t="n">
-        <v>6818975</v>
+        <v>6818635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125937741</v>
+        <v>125937533</v>
       </c>
       <c r="B7" t="n">
         <v>78980</v>
@@ -1191,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488731</v>
+        <v>488556</v>
       </c>
       <c r="R7" t="n">
-        <v>6818925</v>
+        <v>6818975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,19 +1245,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125936168</v>
+        <v>125937741</v>
       </c>
       <c r="B8" t="n">
         <v>78980</v>
@@ -1288,17 +1288,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488761</v>
+        <v>488731</v>
       </c>
       <c r="R8" t="n">
-        <v>6818718</v>
+        <v>6818925</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937321</v>
+        <v>125935502</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488500</v>
+        <v>488799</v>
       </c>
       <c r="R9" t="n">
-        <v>6818934</v>
+        <v>6818778</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125934921</v>
+        <v>125936168</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488878</v>
+        <v>488761</v>
       </c>
       <c r="R10" t="n">
-        <v>6818893</v>
+        <v>6818718</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936684</v>
+        <v>125937321</v>
       </c>
       <c r="B11" t="n">
         <v>78739</v>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488631</v>
+        <v>488500</v>
       </c>
       <c r="R11" t="n">
-        <v>6818621</v>
+        <v>6818934</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,19 +1633,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125935570</v>
+        <v>125934921</v>
       </c>
       <c r="B12" t="n">
         <v>78739</v>
@@ -1676,17 +1676,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488824</v>
+        <v>488878</v>
       </c>
       <c r="R12" t="n">
-        <v>6818805</v>
+        <v>6818893</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125934762</v>
+        <v>125934407</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>78647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488830</v>
+        <v>488897</v>
       </c>
       <c r="R13" t="n">
-        <v>6818872</v>
+        <v>6818851</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125934407</v>
+        <v>125934762</v>
       </c>
       <c r="B14" t="n">
-        <v>78647</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488897</v>
+        <v>488830</v>
       </c>
       <c r="R14" t="n">
-        <v>6818851</v>
+        <v>6818872</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,60 +1924,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125937897</v>
+        <v>125934507</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>92535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488805</v>
+        <v>488909</v>
       </c>
       <c r="R15" t="n">
-        <v>6818928</v>
+        <v>6818877</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2007,11 +2007,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2026,54 +2021,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125934507</v>
+        <v>125935510</v>
       </c>
       <c r="B16" t="n">
-        <v>92535</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488909</v>
+        <v>488703</v>
       </c>
       <c r="R16" t="n">
         <v>6818877</v>
@@ -2123,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125935510</v>
+        <v>125937897</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488703</v>
+        <v>488805</v>
       </c>
       <c r="R17" t="n">
-        <v>6818877</v>
+        <v>6818928</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,6 +2201,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125934896</v>
+        <v>125936426</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488838</v>
+        <v>488720</v>
       </c>
       <c r="R18" t="n">
-        <v>6818893</v>
+        <v>6818745</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2334,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125936426</v>
+        <v>125934896</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,13 +2364,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488720</v>
+        <v>488838</v>
       </c>
       <c r="R19" t="n">
-        <v>6818745</v>
+        <v>6818893</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125934949</v>
+        <v>125937715</v>
       </c>
       <c r="B24" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,37 +2830,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488893</v>
+        <v>488709</v>
       </c>
       <c r="R24" t="n">
-        <v>6818884</v>
+        <v>6818925</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,19 +2904,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125937715</v>
+        <v>125936468</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488709</v>
+        <v>488715</v>
       </c>
       <c r="R25" t="n">
-        <v>6818925</v>
+        <v>6818694</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125936468</v>
+        <v>125934949</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488715</v>
+        <v>488893</v>
       </c>
       <c r="R26" t="n">
-        <v>6818694</v>
+        <v>6818884</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,22 +3098,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125937098</v>
+        <v>125937037</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>78647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488445</v>
+        <v>488431</v>
       </c>
       <c r="R27" t="n">
-        <v>6818739</v>
+        <v>6818719</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3181,11 +3181,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3200,22 +3195,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125937037</v>
+        <v>125937098</v>
       </c>
       <c r="B28" t="n">
-        <v>78647</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3223,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3247,13 +3242,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488431</v>
+        <v>488445</v>
       </c>
       <c r="R28" t="n">
-        <v>6818719</v>
+        <v>6818739</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3283,6 +3278,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3297,12 +3297,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125935283</v>
+        <v>125934563</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3611,37 +3611,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488789</v>
+        <v>488882</v>
       </c>
       <c r="R32" t="n">
-        <v>6818951</v>
+        <v>6818866</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3685,12 +3685,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125934563</v>
+        <v>125935283</v>
       </c>
       <c r="B34" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,37 +3805,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488882</v>
+        <v>488789</v>
       </c>
       <c r="R34" t="n">
-        <v>6818866</v>
+        <v>6818951</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3879,12 +3879,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125934450</v>
+        <v>125935216</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488874</v>
+        <v>488832</v>
       </c>
       <c r="R36" t="n">
-        <v>6818886</v>
+        <v>6818964</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125935216</v>
+        <v>125934450</v>
       </c>
       <c r="B37" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488832</v>
+        <v>488874</v>
       </c>
       <c r="R37" t="n">
-        <v>6818964</v>
+        <v>6818886</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4182,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125933758</v>
+        <v>125934468</v>
       </c>
       <c r="B38" t="n">
-        <v>91210</v>
+        <v>78647</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488841</v>
+        <v>488919</v>
       </c>
       <c r="R38" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125934468</v>
+        <v>125933758</v>
       </c>
       <c r="B39" t="n">
-        <v>78647</v>
+        <v>91210</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488919</v>
+        <v>488841</v>
       </c>
       <c r="R39" t="n">
-        <v>6818878</v>
+        <v>6819005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125935887</v>
+        <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>79598</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488851</v>
+        <v>488895</v>
       </c>
       <c r="R41" t="n">
-        <v>6818708</v>
+        <v>6818859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B42" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R42" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125936025</v>
+        <v>125935887</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,34 +4678,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488845</v>
+        <v>488851</v>
       </c>
       <c r="R43" t="n">
-        <v>6818675</v>
+        <v>6818708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4743,6 +4738,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125934928</v>
+        <v>125936488</v>
       </c>
       <c r="B45" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,37 +4877,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488878</v>
+        <v>488717</v>
       </c>
       <c r="R45" t="n">
-        <v>6818892</v>
+        <v>6818649</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125936488</v>
+        <v>125934928</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,37 +4974,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488717</v>
+        <v>488878</v>
       </c>
       <c r="R46" t="n">
-        <v>6818649</v>
+        <v>6818892</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5048,12 +5048,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R48" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R49" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125936503</v>
+        <v>125934363</v>
       </c>
       <c r="B50" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488698</v>
+        <v>488904</v>
       </c>
       <c r="R50" t="n">
-        <v>6818639</v>
+        <v>6818858</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125934363</v>
+        <v>125936503</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5459,37 +5459,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488904</v>
+        <v>488698</v>
       </c>
       <c r="R51" t="n">
-        <v>6818858</v>
+        <v>6818639</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125984672</v>
+        <v>125984501</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488239</v>
+        <v>488242</v>
       </c>
       <c r="R54" t="n">
-        <v>6818981</v>
+        <v>6819007</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125984501</v>
+        <v>125984672</v>
       </c>
       <c r="B55" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5847,21 +5847,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488242</v>
+        <v>488239</v>
       </c>
       <c r="R55" t="n">
-        <v>6819007</v>
+        <v>6818981</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6127,54 +6127,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125984440</v>
+        <v>125986131</v>
       </c>
       <c r="B58" t="n">
-        <v>98395</v>
+        <v>78738</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488244</v>
+        <v>488444</v>
       </c>
       <c r="R58" t="n">
-        <v>6819028</v>
+        <v>6818918</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6330,45 +6321,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125986131</v>
+        <v>125984440</v>
       </c>
       <c r="B60" t="n">
-        <v>78738</v>
+        <v>98395</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488444</v>
+        <v>488244</v>
       </c>
       <c r="R60" t="n">
-        <v>6818918</v>
+        <v>6819028</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125988445</v>
+        <v>125989085</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488400</v>
+        <v>488202</v>
       </c>
       <c r="R61" t="n">
-        <v>6818592</v>
+        <v>6818963</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125987243</v>
+        <v>125988445</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488354</v>
+        <v>488400</v>
       </c>
       <c r="R62" t="n">
-        <v>6818765</v>
+        <v>6818592</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R63" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7203,10 +7203,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125986843</v>
+        <v>125988482</v>
       </c>
       <c r="B69" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7214,37 +7214,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488440</v>
+        <v>488376</v>
       </c>
       <c r="R69" t="n">
-        <v>6818890</v>
+        <v>6818620</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7288,19 +7288,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125988482</v>
+        <v>125989221</v>
       </c>
       <c r="B70" t="n">
         <v>78980</v>
@@ -7331,17 +7331,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488376</v>
+        <v>488211</v>
       </c>
       <c r="R70" t="n">
-        <v>6818620</v>
+        <v>6818972</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7385,22 +7385,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125989221</v>
+        <v>125986843</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488211</v>
+        <v>488440</v>
       </c>
       <c r="R71" t="n">
-        <v>6818972</v>
+        <v>6818890</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988605</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488257</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
-        <v>6818880</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7579,19 +7579,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985280</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
         <v>78739</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488376</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
         <v>78739</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125986283</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
         <v>78739</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488483</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,22 +7870,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125988576</v>
+        <v>125988605</v>
       </c>
       <c r="B76" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488336</v>
+        <v>488257</v>
       </c>
       <c r="R76" t="n">
-        <v>6818701</v>
+        <v>6818880</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7967,22 +7967,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125987019</v>
+        <v>125985190</v>
       </c>
       <c r="B77" t="n">
-        <v>57817</v>
+        <v>78738</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7990,37 +7990,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488514</v>
+        <v>488327</v>
       </c>
       <c r="R77" t="n">
-        <v>6818802</v>
+        <v>6818968</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8064,22 +8064,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125985190</v>
+        <v>125983993</v>
       </c>
       <c r="B78" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8087,21 +8087,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8111,13 +8111,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488327</v>
+        <v>488175</v>
       </c>
       <c r="R78" t="n">
-        <v>6818968</v>
+        <v>6819105</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8161,22 +8161,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125983993</v>
+        <v>125987019</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8184,34 +8184,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488175</v>
+        <v>488514</v>
       </c>
       <c r="R79" t="n">
-        <v>6819105</v>
+        <v>6818802</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8270,54 +8270,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125989375</v>
+        <v>125987994</v>
       </c>
       <c r="B80" t="n">
-        <v>98395</v>
+        <v>78738</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488248</v>
+        <v>488450</v>
       </c>
       <c r="R80" t="n">
-        <v>6819009</v>
+        <v>6818611</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8376,7 +8367,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125984338</v>
+        <v>125989375</v>
       </c>
       <c r="B81" t="n">
         <v>98395</v>
@@ -8406,7 +8397,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8420,10 +8411,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488234</v>
+        <v>488248</v>
       </c>
       <c r="R81" t="n">
-        <v>6819040</v>
+        <v>6819009</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8482,45 +8473,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125987994</v>
+        <v>125984338</v>
       </c>
       <c r="B82" t="n">
-        <v>78738</v>
+        <v>98395</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488450</v>
+        <v>488234</v>
       </c>
       <c r="R82" t="n">
-        <v>6818611</v>
+        <v>6819040</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R48" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B49" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R49" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125989085</v>
+        <v>125988445</v>
       </c>
       <c r="B61" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488202</v>
+        <v>488400</v>
       </c>
       <c r="R61" t="n">
-        <v>6818963</v>
+        <v>6818592</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125988445</v>
+        <v>125987243</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488400</v>
+        <v>488354</v>
       </c>
       <c r="R62" t="n">
-        <v>6818592</v>
+        <v>6818765</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125987243</v>
+        <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488354</v>
+        <v>488202</v>
       </c>
       <c r="R63" t="n">
-        <v>6818765</v>
+        <v>6818963</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988576</v>
       </c>
       <c r="B72" t="n">
         <v>78739</v>
@@ -7525,14 +7525,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488336</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
         <v>78739</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
         <v>78739</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
         <v>78739</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936684</v>
+        <v>125936168</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488631</v>
+        <v>488761</v>
       </c>
       <c r="R4" t="n">
-        <v>6818621</v>
+        <v>6818718</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125935570</v>
+        <v>125936665</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488824</v>
+        <v>488458</v>
       </c>
       <c r="R5" t="n">
-        <v>6818805</v>
+        <v>6818635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125936665</v>
+        <v>125937533</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488458</v>
+        <v>488556</v>
       </c>
       <c r="R6" t="n">
-        <v>6818635</v>
+        <v>6818975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125937533</v>
+        <v>125937741</v>
       </c>
       <c r="B7" t="n">
         <v>78980</v>
@@ -1191,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488556</v>
+        <v>488731</v>
       </c>
       <c r="R7" t="n">
-        <v>6818975</v>
+        <v>6818925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125937741</v>
+        <v>125935502</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488731</v>
+        <v>488799</v>
       </c>
       <c r="R8" t="n">
-        <v>6818925</v>
+        <v>6818778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125935502</v>
+        <v>125937321</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488799</v>
+        <v>488500</v>
       </c>
       <c r="R9" t="n">
-        <v>6818778</v>
+        <v>6818934</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125936168</v>
+        <v>125934921</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488761</v>
+        <v>488878</v>
       </c>
       <c r="R10" t="n">
-        <v>6818718</v>
+        <v>6818893</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125937321</v>
+        <v>125936684</v>
       </c>
       <c r="B11" t="n">
         <v>78739</v>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488500</v>
+        <v>488631</v>
       </c>
       <c r="R11" t="n">
-        <v>6818934</v>
+        <v>6818621</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,19 +1633,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125934921</v>
+        <v>125935570</v>
       </c>
       <c r="B12" t="n">
         <v>78739</v>
@@ -1676,17 +1676,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488878</v>
+        <v>488824</v>
       </c>
       <c r="R12" t="n">
-        <v>6818893</v>
+        <v>6818805</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125934399</v>
+        <v>125935887</v>
       </c>
       <c r="B41" t="n">
-        <v>79598</v>
+        <v>57657</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488895</v>
+        <v>488851</v>
       </c>
       <c r="R41" t="n">
-        <v>6818859</v>
+        <v>6818708</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4570,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125936025</v>
+        <v>125934399</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,34 +4586,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488845</v>
+        <v>488895</v>
       </c>
       <c r="R42" t="n">
-        <v>6818675</v>
+        <v>6818859</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125935887</v>
+        <v>125936025</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,34 +4683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488851</v>
+        <v>488845</v>
       </c>
       <c r="R43" t="n">
-        <v>6818708</v>
+        <v>6818675</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4738,11 +4743,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R48" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R49" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125988445</v>
+        <v>125989085</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488400</v>
+        <v>488202</v>
       </c>
       <c r="R61" t="n">
-        <v>6818592</v>
+        <v>6818963</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125987243</v>
+        <v>125988445</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488354</v>
+        <v>488400</v>
       </c>
       <c r="R62" t="n">
-        <v>6818765</v>
+        <v>6818592</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125989085</v>
+        <v>125987243</v>
       </c>
       <c r="B63" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488202</v>
+        <v>488354</v>
       </c>
       <c r="R63" t="n">
-        <v>6818963</v>
+        <v>6818765</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125988576</v>
+        <v>125985280</v>
       </c>
       <c r="B72" t="n">
         <v>78739</v>
@@ -7525,14 +7525,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488336</v>
+        <v>488376</v>
       </c>
       <c r="R72" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985280</v>
+        <v>125985181</v>
       </c>
       <c r="B73" t="n">
         <v>78739</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488376</v>
+        <v>488320</v>
       </c>
       <c r="R73" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125985181</v>
+        <v>125986283</v>
       </c>
       <c r="B74" t="n">
         <v>78739</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488320</v>
+        <v>488483</v>
       </c>
       <c r="R74" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125986283</v>
+        <v>125988576</v>
       </c>
       <c r="B75" t="n">
         <v>78739</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488483</v>
+        <v>488336</v>
       </c>
       <c r="R75" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 26180-2025 artfynd.xlsx
+++ b/artfynd/A 26180-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125936168</v>
+        <v>125936684</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488761</v>
+        <v>488631</v>
       </c>
       <c r="R4" t="n">
-        <v>6818718</v>
+        <v>6818621</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125936665</v>
+        <v>125935570</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488458</v>
+        <v>488824</v>
       </c>
       <c r="R5" t="n">
-        <v>6818635</v>
+        <v>6818805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125937533</v>
+        <v>125936665</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488556</v>
+        <v>488458</v>
       </c>
       <c r="R6" t="n">
-        <v>6818975</v>
+        <v>6818635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125937741</v>
+        <v>125937533</v>
       </c>
       <c r="B7" t="n">
         <v>78980</v>
@@ -1191,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488731</v>
+        <v>488556</v>
       </c>
       <c r="R7" t="n">
-        <v>6818925</v>
+        <v>6818975</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125935502</v>
+        <v>125937741</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488799</v>
+        <v>488731</v>
       </c>
       <c r="R8" t="n">
-        <v>6818778</v>
+        <v>6818925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125937321</v>
+        <v>125935502</v>
       </c>
       <c r="B9" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488500</v>
+        <v>488799</v>
       </c>
       <c r="R9" t="n">
-        <v>6818934</v>
+        <v>6818778</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125934921</v>
+        <v>125936168</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488878</v>
+        <v>488761</v>
       </c>
       <c r="R10" t="n">
-        <v>6818893</v>
+        <v>6818718</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125936684</v>
+        <v>125937321</v>
       </c>
       <c r="B11" t="n">
         <v>78739</v>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488631</v>
+        <v>488500</v>
       </c>
       <c r="R11" t="n">
-        <v>6818621</v>
+        <v>6818934</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,19 +1633,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125935570</v>
+        <v>125934921</v>
       </c>
       <c r="B12" t="n">
         <v>78739</v>
@@ -1676,17 +1676,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488824</v>
+        <v>488878</v>
       </c>
       <c r="R12" t="n">
-        <v>6818805</v>
+        <v>6818893</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125935887</v>
+        <v>125934399</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>79598</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,34 +4484,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488851</v>
+        <v>488895</v>
       </c>
       <c r="R41" t="n">
-        <v>6818708</v>
+        <v>6818859</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125934399</v>
+        <v>125936025</v>
       </c>
       <c r="B42" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,34 +4581,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488895</v>
+        <v>488845</v>
       </c>
       <c r="R42" t="n">
-        <v>6818859</v>
+        <v>6818675</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125936025</v>
+        <v>125935887</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4683,34 +4678,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488845</v>
+        <v>488851</v>
       </c>
       <c r="R43" t="n">
-        <v>6818675</v>
+        <v>6818708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4743,6 +4738,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5157,10 +5157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125936642</v>
+        <v>125935420</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5168,34 +5168,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488637</v>
+        <v>488729</v>
       </c>
       <c r="R48" t="n">
-        <v>6818637</v>
+        <v>6818892</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125935420</v>
+        <v>125936642</v>
       </c>
       <c r="B49" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488729</v>
+        <v>488637</v>
       </c>
       <c r="R49" t="n">
-        <v>6818892</v>
+        <v>6818637</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125989085</v>
+        <v>125988445</v>
       </c>
       <c r="B61" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,37 +6438,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488202</v>
+        <v>488400</v>
       </c>
       <c r="R61" t="n">
-        <v>6818963</v>
+        <v>6818592</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,19 +6512,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125988445</v>
+        <v>125987243</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -6555,17 +6555,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488400</v>
+        <v>488354</v>
       </c>
       <c r="R62" t="n">
-        <v>6818592</v>
+        <v>6818765</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125987243</v>
+        <v>125989085</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,21 +6632,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,13 +6656,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488354</v>
+        <v>488202</v>
       </c>
       <c r="R63" t="n">
-        <v>6818765</v>
+        <v>6818963</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7494,7 +7494,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125985280</v>
+        <v>125988576</v>
       </c>
       <c r="B72" t="n">
         <v>78739</v>
@@ -7525,14 +7525,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488376</v>
+        <v>488336</v>
       </c>
       <c r="R72" t="n">
-        <v>6818970</v>
+        <v>6818701</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125985181</v>
+        <v>125985280</v>
       </c>
       <c r="B73" t="n">
         <v>78739</v>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488320</v>
+        <v>488376</v>
       </c>
       <c r="R73" t="n">
-        <v>6818956</v>
+        <v>6818970</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125986283</v>
+        <v>125985181</v>
       </c>
       <c r="B74" t="n">
         <v>78739</v>
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488483</v>
+        <v>488320</v>
       </c>
       <c r="R74" t="n">
-        <v>6818970</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7773,19 +7773,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125988576</v>
+        <v>125986283</v>
       </c>
       <c r="B75" t="n">
         <v>78739</v>
@@ -7816,17 +7816,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488336</v>
+        <v>488483</v>
       </c>
       <c r="R75" t="n">
-        <v>6818701</v>
+        <v>6818970</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7870,12 +7870,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8270,45 +8270,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125987994</v>
+        <v>125989375</v>
       </c>
       <c r="B80" t="n">
-        <v>78738</v>
+        <v>98395</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>219874</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488450</v>
+        <v>488248</v>
       </c>
       <c r="R80" t="n">
-        <v>6818611</v>
+        <v>6819009</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8367,7 +8376,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125989375</v>
+        <v>125984338</v>
       </c>
       <c r="B81" t="n">
         <v>98395</v>
@@ -8397,7 +8406,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8411,10 +8420,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488248</v>
+        <v>488234</v>
       </c>
       <c r="R81" t="n">
-        <v>6819009</v>
+        <v>6819040</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8473,54 +8482,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125984338</v>
+        <v>125987994</v>
       </c>
       <c r="B82" t="n">
-        <v>98395</v>
+        <v>78738</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488234</v>
+        <v>488450</v>
       </c>
       <c r="R82" t="n">
-        <v>6819040</v>
+        <v>6818611</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
